--- a/metrics/Metrics_Augmented_Model.xlsx
+++ b/metrics/Metrics_Augmented_Model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:AS61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.646209549864779</v>
+        <v>2.685188861513206</v>
       </c>
       <c r="C2" t="n">
-        <v>2.736597822145525</v>
+        <v>2.756133110443068</v>
       </c>
       <c r="D2" t="n">
-        <v>9.261410569429403</v>
+        <v>9.627509833596291</v>
       </c>
       <c r="E2" t="n">
-        <v>3.043256573052854</v>
+        <v>3.102822881441397</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8838430263072209</v>
+        <v>0.8918665495997403</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9403349021502477</v>
+        <v>0.9447223928853239</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9458143642914911</v>
+        <v>0.950861679267575</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8021268382267586</v>
+        <v>0.8117996948252215</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008573333750833911</v>
+        <v>3.607900803189277</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09685332538280922</v>
+        <v>4.105650888800407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4724200844209087</v>
+        <v>14.90696177369608</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4732663174892558</v>
+        <v>3.860953479866869</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3955828473471034</v>
+        <v>0.8398488491161371</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1081913829578562</v>
+        <v>0.9601516324408801</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1755066918207735</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9603532713829624</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8593481108318176</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.240963744587607</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.852769528532265</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7.52803078304034</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.743725712063861</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8983747602176986</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9478863251399923</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9453268996322541</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8104581175292442</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.613989547338792</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.614839264158239</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.956985918518914</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.992822400096423</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.8933849928106923</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.953796718814875</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9636537856578024</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8471607684567377</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.01568808409310168</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1746996369293408</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.008356171918990019</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.007857861571049229</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.0163435413281639</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.2076508597034441</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.3368080206210515</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>2</v>
       </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.678792973795274</v>
+        <v>2.724006018003726</v>
       </c>
       <c r="C3" t="n">
-        <v>2.658875870410956</v>
+        <v>2.685362101570268</v>
       </c>
       <c r="D3" t="n">
-        <v>9.397686602492767</v>
+        <v>9.842477133035</v>
       </c>
       <c r="E3" t="n">
-        <v>3.065564646601465</v>
+        <v>3.137272244009914</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8821338469690596</v>
+        <v>0.889452098073509</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9395223952416369</v>
+        <v>0.9436819707798136</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9459342572368469</v>
+        <v>0.9504528514828847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8024337962684583</v>
+        <v>0.8115079822277009</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009463660240993266</v>
+        <v>3.679590095558294</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1231112877318932</v>
+        <v>4.002874645353787</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4729398794895192</v>
+        <v>15.05645519553661</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4736490357662652</v>
+        <v>3.880264835747248</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3964249900561895</v>
+        <v>0.8382427845188848</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1215813511053159</v>
+        <v>0.9531862673159782</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1935615136170652</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9545684356925633</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.8507867348833063</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.284365623957699</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.99703400010301</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7.71689982046939</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.777930852355651</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8958251078890417</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9468007623241763</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9424576811325348</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.8056291714466469</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.638125100308792</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.452400434691828</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.211291445056922</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.035010946447627</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.8903579940203878</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.952696207546383</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.964654288470793</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8513789963494683</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.01543414652023511</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1916281460784157</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.007549315510513799</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.008350298534035627</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01658648687567543</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.1802841797303507</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.3650471451090023</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.678369900859158</v>
+        <v>2.73145477879197</v>
       </c>
       <c r="C4" t="n">
-        <v>2.556814994113014</v>
+        <v>2.569574946392301</v>
       </c>
       <c r="D4" t="n">
-        <v>9.433728769552879</v>
+        <v>9.950024853432618</v>
       </c>
       <c r="E4" t="n">
-        <v>3.07143757376784</v>
+        <v>3.154365998648955</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8816818046997262</v>
+        <v>0.88824415268677</v>
       </c>
       <c r="G4" t="n">
-        <v>0.939336543214754</v>
+        <v>0.943205039084919</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9463156352643826</v>
+        <v>0.950328759164132</v>
       </c>
       <c r="I4" t="n">
-        <v>0.802502009166614</v>
+        <v>0.8101223473894779</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00912102541985238</v>
+        <v>3.755989954557436</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1041208911448654</v>
+        <v>3.93108497067223</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4732955323371875</v>
+        <v>15.41937211316048</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4737849476807659</v>
+        <v>3.926750834107059</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3968769432446513</v>
+        <v>0.8343438302641523</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1144288626595191</v>
+        <v>0.9454953058005277</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1607880511585886</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9484308661186035</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.8379446709605394</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.335632092330305</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.182418132369031</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7.848063254742958</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.801439496891367</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8940544568591933</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9461751704177244</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9424899195426442</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8048243470995474</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.594427387813123</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.420322790846418</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.211925313578316</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.03511537071959</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8903504490831087</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9525656430856143</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.9641082513423473</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8471607684567377</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01732345770820359</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1883841055004165</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.008102870671835738</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.0093799682063751</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01799221558273961</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1846443300922804</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.2997438883392161</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -742,67 +1078,139 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.572229574514709</v>
+        <v>2.587743976597983</v>
       </c>
       <c r="C5" t="n">
-        <v>2.512405506484842</v>
+        <v>2.525697187807511</v>
       </c>
       <c r="D5" t="n">
-        <v>8.816493821663858</v>
+        <v>9.10220271769192</v>
       </c>
       <c r="E5" t="n">
-        <v>2.969258126479383</v>
+        <v>3.016985700611112</v>
       </c>
       <c r="F5" t="n">
-        <v>0.889423189564022</v>
+        <v>0.8977666496198231</v>
       </c>
       <c r="G5" t="n">
-        <v>0.94357853503864</v>
+        <v>0.9482121677512279</v>
       </c>
       <c r="H5" t="n">
-        <v>0.94958654275345</v>
+        <v>0.9543597289220129</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8106420816798356</v>
+        <v>0.8198217912570388</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00750399012599462</v>
+        <v>3.837662621341097</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1255843434056205</v>
+        <v>3.685679365965568</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4747627740278275</v>
+        <v>16.16257554778207</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4758417368106409</v>
+        <v>4.020270581413901</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4010945194198416</v>
+        <v>0.8263593135529396</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1247266283955033</v>
+        <v>0.9275675986874445</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2460995564727206</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+        <v>0.9362262737473954</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.8165412310892612</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.349374856431242</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.456637635557446</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7.523825556806606</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.742959269986816</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8984315289978296</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9490705148474119</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.9472289658286974</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.8128725905705428</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.275067582245159</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.977348040965957</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7.473994048764452</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.73386064911225</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9110370456657336</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.9610146234658826</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.9681713102235764</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8570033002064424</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.0172276116350687</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.2065396595620823</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.008259953547660459</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.008917619756282968</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.01813789072606758</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.1955263033675769</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.2808056466485154</v>
+      </c>
+      <c r="AO5" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="AQ5" t="n">
         <v>7</v>
       </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -811,67 +1219,139 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.67858603290349</v>
+        <v>2.692225203201924</v>
       </c>
       <c r="C6" t="n">
-        <v>2.727801576809836</v>
+        <v>2.756027002020859</v>
       </c>
       <c r="D6" t="n">
-        <v>9.327665116878451</v>
+        <v>9.427670735402655</v>
       </c>
       <c r="E6" t="n">
-        <v>3.054122642736937</v>
+        <v>3.070451226677059</v>
       </c>
       <c r="F6" t="n">
-        <v>0.883012059181061</v>
+        <v>0.8941110854751695</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9423638692713094</v>
+        <v>0.9480261422541491</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9456283632013652</v>
+        <v>0.9506112384060925</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8015242909597186</v>
+        <v>0.8122372637215026</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009801063175702118</v>
+        <v>3.781558464914477</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1010893390845962</v>
+        <v>4.082535766611018</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4680039957059559</v>
+        <v>16.87987748233726</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4699427976393207</v>
+        <v>4.108512806641506</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3895230052155986</v>
+        <v>0.8186530664923923</v>
       </c>
       <c r="O6" t="n">
-        <v>0.110791414499757</v>
+        <v>0.9608036897857088</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1602765789542917</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>0.9615525665870697</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.8614884548189454</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.16304367563842</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.955631406624794</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6.704229195909913</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.58925263269344</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.9094957341135251</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9563663470208575</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.9535154557999925</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.823335307082837</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.610988893030188</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.695992848725562</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8.338337627785753</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.887617985084896</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.9007487636778319</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.9695100443564406</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.9710473318690542</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8710640598488779</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.01531672485038338</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1575604389540435</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.009965741710856124</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.009047650822751607</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.018203738385344</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.1811882276990371</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.1952856482801291</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -880,67 +1360,139 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.616080876638927</v>
+        <v>2.639661024970769</v>
       </c>
       <c r="C7" t="n">
-        <v>2.726954682396606</v>
+        <v>2.751908915811571</v>
       </c>
       <c r="D7" t="n">
-        <v>9.113837724765792</v>
+        <v>9.250471577078921</v>
       </c>
       <c r="E7" t="n">
-        <v>3.018913335086947</v>
+        <v>3.041458790955242</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8856938906984337</v>
+        <v>0.8961013359894512</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9441197909188644</v>
+        <v>0.949203193921677</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9473544454577421</v>
+        <v>0.9516838472849106</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8047871412548228</v>
+        <v>0.8147168208004278</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01159759312522946</v>
+        <v>3.507506154870384</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1265111841900419</v>
+        <v>4.03793196170639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4690212444396476</v>
+        <v>15.93796408717271</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4707723967771027</v>
+        <v>3.992237979776846</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3901874198192746</v>
+        <v>0.8287723997648977</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1390014318732857</v>
+        <v>0.9746954098890224</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1840156594344604</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>0.9724873169774582</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.8807515507030957</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.150422787758961</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.807670162811469</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6.696011466542777</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.587665253958243</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.9096066699932353</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.9564205851047271</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.954063508771849</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.8257497801241356</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.615197945331655</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.69806330388015</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.338665440834918</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.887674746372056</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.9007448617189685</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.9688109026427653</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.9706199984641837</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8705016294631804</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.0145984560859887</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1804238335897128</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.007768985534654216</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.008330470732284156</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.01749563850437391</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.1857816595762118</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.2341580904852321</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>3</v>
       </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -949,67 +1501,139 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.612204084454242</v>
+        <v>2.637312166882583</v>
       </c>
       <c r="C8" t="n">
-        <v>2.755602304808637</v>
+        <v>2.759875912123618</v>
       </c>
       <c r="D8" t="n">
-        <v>9.070722069686564</v>
+        <v>9.2232712304705</v>
       </c>
       <c r="E8" t="n">
-        <v>3.011763946541389</v>
+        <v>3.036983903558018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8862346489312365</v>
+        <v>0.8964068425411649</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9443139653323452</v>
+        <v>0.9492419485088032</v>
       </c>
       <c r="H8" t="n">
-        <v>0.947764652812105</v>
+        <v>0.9520989924967377</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8057193841962811</v>
+        <v>0.8157378148917501</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01123472222470706</v>
+        <v>3.519079253967538</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09677805556007835</v>
+        <v>4.02033124426001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4689674403587965</v>
+        <v>15.87730811106075</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4705498327927542</v>
+        <v>3.984633999636699</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3902948409830647</v>
+        <v>0.8294240499488712</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09416924066538557</v>
+        <v>0.9738218040693797</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1266286768257852</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>0.9724873169774582</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.8807515507030957</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.152838267276362</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.759355320181003</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.749878433712983</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.598052815805133</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.9088794886608541</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.9560227347555975</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.954063508771849</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.8241401314299365</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.604951579609112</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.732140421122624</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.275392376095047</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.876698172574774</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9014980010354191</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.9685970726334837</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.9704911201357307</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.8707828446560293</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.01465632932724709</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.171493345116825</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.008789407484589451</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.00709373676370928</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.01546126743684489</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.1832801977396976</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.2470046941147783</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>4</v>
       </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1018,67 +1642,139 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884916632104194</v>
+        <v>2.923363717589878</v>
       </c>
       <c r="C9" t="n">
-        <v>2.850647353221365</v>
+        <v>2.852825929326108</v>
       </c>
       <c r="D9" t="n">
-        <v>11.43444788459109</v>
+        <v>11.72245627737639</v>
       </c>
       <c r="E9" t="n">
-        <v>3.381486046783439</v>
+        <v>3.423807278071648</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8565887072854679</v>
+        <v>0.8683367073783197</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9273657103235692</v>
+        <v>0.9336683482588274</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9343555349838144</v>
+        <v>0.9402258394384861</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7797416388153989</v>
+        <v>0.7905776033555958</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01535621347640587</v>
+        <v>5.110577243268006</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1668572523443914</v>
+        <v>4.915359972953283</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4619676870959581</v>
+        <v>29.39188663903225</v>
       </c>
       <c r="M9" t="n">
-        <v>0.464311300417532</v>
+        <v>5.421428468497233</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3798338123168798</v>
+        <v>0.6842318009968344</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1471072892664138</v>
+        <v>0.8929136247157616</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1104426537689656</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>0.9114643551214189</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.7865764152694719</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.153972463288406</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.881575342773051</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.913318711551677</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.629319058530493</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.9066731138592443</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.9558882390465645</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.9524515882663888</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.8217256583886378</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.585832933952426</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.760889009302655</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.158844449496399</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.856369102461445</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9028852710551836</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.9675357977247753</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.9699518660772035</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.8688143383060883</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.02184153316270843</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.2492478801147318</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.01204281259769258</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.01072751687402945</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.02088446180061876</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.2000797090944157</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.1352977539162474</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>7</v>
       </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1087,67 +1783,139 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.495193678595416</v>
+        <v>2.367948900336166</v>
       </c>
       <c r="C10" t="n">
-        <v>2.554634801595387</v>
+        <v>2.345298789244495</v>
       </c>
       <c r="D10" t="n">
-        <v>8.295603945717904</v>
+        <v>7.430948755652185</v>
       </c>
       <c r="E10" t="n">
-        <v>2.880209010769514</v>
+        <v>2.725976660878113</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8959562107667325</v>
+        <v>0.9165376984719181</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9467291306218438</v>
+        <v>0.9576124867936335</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9489792461063351</v>
+        <v>0.959047259857294</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8091186602876964</v>
+        <v>0.8336052114898886</v>
       </c>
       <c r="J10" t="n">
-        <v>0.009213142993294676</v>
+        <v>3.310892056109725</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1146497098503105</v>
+        <v>3.653700706830618</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4744611821814391</v>
+        <v>12.79054851307151</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4759088840105631</v>
+        <v>3.576387634621212</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4007431247654101</v>
+        <v>0.8625862804304764</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1180029783393817</v>
+        <v>0.9584170833854189</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1514102760658314</v>
-      </c>
-      <c r="Q10" t="inlineStr">
+        <v>0.9655031860829518</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.8721901747545845</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.386038769682499</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.555467942893951</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6.730152811363853</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.594253806273367</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.9091457762410804</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.9539133455308306</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.9490020783847037</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.8096532931821445</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.014296260278542</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.826814386991968</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.899005934679541</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.428786926570452</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9297841298560818</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.9728696169442898</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.9738690889551832</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.8755635029344573</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.01431622145431921</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1509692304989887</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.007644550609561152</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.008045743660330396</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.01710129115093889</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.1644892776530733</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.1606866461033947</v>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1156,67 +1924,139 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.496500580391048</v>
+        <v>2.43215718135348</v>
       </c>
       <c r="C11" t="n">
-        <v>2.446649763695798</v>
+        <v>2.3853061024957</v>
       </c>
       <c r="D11" t="n">
-        <v>8.291679736384877</v>
+        <v>7.827893823738949</v>
       </c>
       <c r="E11" t="n">
-        <v>2.879527693283202</v>
+        <v>2.797837347620292</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8960054283537128</v>
+        <v>0.9120793244402653</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9468482914270003</v>
+        <v>0.9552738363137049</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9498012608848073</v>
+        <v>0.9567125192855628</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8101418537600287</v>
+        <v>0.8283543847345174</v>
       </c>
       <c r="J11" t="n">
-        <v>0.008572905674845532</v>
+        <v>3.484153350056627</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1070637626606601</v>
+        <v>3.656527036598112</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4738903875406528</v>
+        <v>13.84903429052205</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4752638428742054</v>
+        <v>3.721429065630843</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3993479101191576</v>
+        <v>0.8512145657896013</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1083727209447063</v>
+        <v>0.9530933618909351</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1203403388806288</v>
-      </c>
-      <c r="Q11" t="inlineStr">
+        <v>0.9628929553446012</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.8636287988060731</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.418102728475855</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.548496008752065</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7.062200799452935</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.657480159747752</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.9046632684802454</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.9512788703633923</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.9472289658286974</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.8072388201408459</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.057976100231584</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.977143571819783</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.094007189111981</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.468604299824494</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9274630298418176</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.971517370670504</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.9733434010364933</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.8752822877416085</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.01635630956388645</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1537866418912248</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.008528572628825448</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.008194802589941652</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.01797977888568353</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.1588022731496022</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.2061307513080961</v>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="AQ11" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1225,67 +2065,139 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.486158394177737</v>
+        <v>2.384485040920207</v>
       </c>
       <c r="C12" t="n">
-        <v>2.42949684876972</v>
+        <v>2.259855717436352</v>
       </c>
       <c r="D12" t="n">
-        <v>8.362799397584162</v>
+        <v>7.390628404400812</v>
       </c>
       <c r="E12" t="n">
-        <v>2.891850514391116</v>
+        <v>2.718571022504435</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8951134427805612</v>
+        <v>0.9169905651817445</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9464602307501691</v>
+        <v>0.9579750460387121</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9493534097843138</v>
+        <v>0.9597236758056947</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8096188882075033</v>
+        <v>0.8347720618799712</v>
       </c>
       <c r="J12" t="n">
-        <v>0.007614093060857197</v>
+        <v>3.29610109572123</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09157972229140787</v>
+        <v>3.575603854966244</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4734600292431387</v>
+        <v>12.30428455056539</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4751296340497244</v>
+        <v>3.5077463634883</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3986930191649439</v>
+        <v>0.8678103988263601</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09710507276238545</v>
+        <v>0.959199315700798</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1071706608897449</v>
-      </c>
-      <c r="Q12" t="inlineStr">
+        <v>0.9736160654048531</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.8850322386773514</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.343410071823181</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.383089564018406</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6.567438584457014</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.562701423197212</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.9113423496614034</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.9549106515115768</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.9505172836598365</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.8136774149176423</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.077429597645339</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.870922332895972</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>6.093676310224879</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.468537281514071</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9274669682933512</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.9720252609989276</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.9738114328608755</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.8769695788987009</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.01362471462914583</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.1481189262590428</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.007064485287302746</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.008904829412754667</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.01824785359945708</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.1509958643511946</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.2392526764563856</v>
+      </c>
+      <c r="AO12" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="AQ12" t="n">
         <v>4</v>
       </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1294,67 +2206,139 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.551448337482594</v>
+        <v>2.442559133589433</v>
       </c>
       <c r="C13" t="n">
-        <v>2.435667120653145</v>
+        <v>2.302108706025795</v>
       </c>
       <c r="D13" t="n">
-        <v>8.70817599171172</v>
+        <v>7.821211629070915</v>
       </c>
       <c r="E13" t="n">
-        <v>2.950961875679135</v>
+        <v>2.79664292126666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.890781716024963</v>
+        <v>0.9121543769489814</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9440136632791494</v>
+        <v>0.9553372064330721</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9465358834613533</v>
+        <v>0.956804121979042</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8029908682700615</v>
+        <v>0.8290107380789387</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009804874119792528</v>
+        <v>3.404041913684161</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1136619359338553</v>
+        <v>3.677608344577443</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4729733191990458</v>
+        <v>13.38855588566038</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4745461117795497</v>
+        <v>3.659037562756139</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3978938729321075</v>
+        <v>0.8561616601482847</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1141935981727351</v>
+        <v>0.9548567262592715</v>
       </c>
       <c r="P13" t="n">
-        <v>0.198176198188845</v>
-      </c>
-      <c r="Q13" t="inlineStr">
+        <v>0.9621874875774793</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.8636287988060731</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.41268877704437</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.529742454954897</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.92808324762786</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.632125234031971</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.9064737988508098</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.9524398637963891</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.9460039062445476</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.8056291714466469</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.110703128193373</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.950842944946812</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6.328171101583008</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.515585637894883</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9246757766923002</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.9706819820307639</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.9728244961877219</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.875844718127306</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.01454024582079266</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.1535270865864207</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.007762077597718631</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.008317730815230517</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.01821176111561412</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.1552334340325816</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.2592548303689057</v>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="AQ13" t="n">
         <v>7</v>
       </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1363,67 +2347,139 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.493135264602211</v>
+        <v>2.370720931749583</v>
       </c>
       <c r="C14" t="n">
-        <v>2.386819624107076</v>
+        <v>2.315617163625365</v>
       </c>
       <c r="D14" t="n">
-        <v>8.412196745641161</v>
+        <v>7.562171757920476</v>
       </c>
       <c r="E14" t="n">
-        <v>2.900378724518776</v>
+        <v>2.7499403189743</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8944938993086747</v>
+        <v>0.9150638390573439</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9461458149019536</v>
+        <v>0.9566792564531136</v>
       </c>
       <c r="H14" t="n">
-        <v>0.948395192577636</v>
+        <v>0.9589931104818382</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8090049721241039</v>
+        <v>0.8330217862948475</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008496361666798458</v>
+        <v>3.29913923608533</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09711427848500254</v>
+        <v>3.425072355802545</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4736740497052492</v>
+        <v>12.67860362886484</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4750098250337341</v>
+        <v>3.560702687513357</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3991009955014762</v>
+        <v>0.8637889468298021</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0956410252373836</v>
+        <v>0.9563080487081489</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1892496186968049</v>
-      </c>
-      <c r="Q14" t="inlineStr">
+        <v>0.9611292859267965</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.8593481108318176</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.47617163591029</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.573717583602163</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.608096096110207</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.758277740930055</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8972939122677538</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.9476281425224616</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.9410391910877296</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.7975809279756514</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.970366749184759</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.783965524297615</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.674324198654257</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.382084003274078</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9324585166553414</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.9706957504178707</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.9743913853389139</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.8769695788987009</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.01848618389892287</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.167401659103217</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.009790291898388093</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.009409343435121287</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.02050535676843995</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.1796275789365438</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.2441856892382883</v>
+      </c>
+      <c r="AO14" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="AP14" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="AQ14" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1432,67 +2488,139 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.388060642135696</v>
+        <v>2.360839979539898</v>
       </c>
       <c r="C15" t="n">
-        <v>2.229538274630651</v>
+        <v>2.296418471494364</v>
       </c>
       <c r="D15" t="n">
-        <v>7.675410771043008</v>
+        <v>7.453723839295253</v>
       </c>
       <c r="E15" t="n">
-        <v>2.770453170700239</v>
+        <v>2.730150882148321</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9037346978271102</v>
+        <v>0.9162818952143732</v>
       </c>
       <c r="G15" t="n">
-        <v>0.951477486087876</v>
+        <v>0.9576839906215691</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9546421175087181</v>
+        <v>0.9602141788983642</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8208740164031589</v>
+        <v>0.8338239959380291</v>
       </c>
       <c r="J15" t="n">
-        <v>0.008711030050538748</v>
+        <v>3.225265034809269</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1064249897989247</v>
+        <v>3.19508806856728</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4750193492596618</v>
+        <v>12.18723637487734</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4764985410522834</v>
+        <v>3.491022253563752</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4019188753130199</v>
+        <v>0.8690678918239189</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1036421336538857</v>
+        <v>0.9534909705742496</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1767242982610679</v>
-      </c>
-      <c r="Q15" t="inlineStr">
+        <v>0.9674079490541809</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.8679094867803289</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.382118960342299</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.589442645832997</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6.986865701247319</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.643267996486039</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.9056802605250198</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.9517640092185535</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.9486474558735024</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.8104581175292442</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.033841722931426</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.857760201221451</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>6.010246437426156</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.451580395872458</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9284600341046805</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.9700887243271039</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.9733264433616969</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.8727513510059702</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.01406425499236796</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.181427229750222</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.007658686565757633</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.009324715749028822</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.02172687871291873</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.1739027138215401</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.2280882312282617</v>
+      </c>
+      <c r="AO15" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="AP15" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="AQ15" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1501,67 +2629,139 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.495279063921822</v>
+        <v>2.380585639564007</v>
       </c>
       <c r="C16" t="n">
-        <v>2.301671823865753</v>
+        <v>2.103404931349787</v>
       </c>
       <c r="D16" t="n">
-        <v>8.517329786981874</v>
+        <v>7.854570440027082</v>
       </c>
       <c r="E16" t="n">
-        <v>2.918446468068564</v>
+        <v>2.802600656537974</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8931753165910955</v>
+        <v>0.9117797002784521</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9458723950349244</v>
+        <v>0.9556345313379951</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9498292761410622</v>
+        <v>0.9586005275097844</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8109717773542537</v>
+        <v>0.8308339418134426</v>
       </c>
       <c r="J16" t="n">
-        <v>0.009303879941981452</v>
+        <v>3.31858345930555</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1263803264576395</v>
+        <v>3.367072064715335</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4728718841499177</v>
+        <v>13.19237989943195</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4743060546477536</v>
+        <v>3.632131591700933</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3978409326453897</v>
+        <v>0.8582692532613023</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1151784366281603</v>
+        <v>0.9521722494124233</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1318845284702794</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+        <v>0.9644449844322692</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.8593481108318176</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.182102683219741</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.055771294968213</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6.1616920224272</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.482275573425964</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.916819757079824</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.9579442310992333</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.9544181312830503</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.8281642531654342</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.157601084094248</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.858979635279091</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>6.920881430550859</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.63075681706821</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9176207453950607</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.9654252421684789</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.9682866224121923</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.8600966673277782</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.01808264217280414</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.1818209066015908</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.01040122738434879</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.008398554144046111</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.01867590470014202</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.1763932217871567</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.2955503499898521</v>
+      </c>
+      <c r="AO16" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="AP16" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="AQ16" t="n">
         <v>4</v>
       </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1570,67 +2770,139 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.550063520097002</v>
+        <v>2.437315475289986</v>
       </c>
       <c r="C17" t="n">
-        <v>2.385743336672324</v>
+        <v>2.30930503146002</v>
       </c>
       <c r="D17" t="n">
-        <v>8.994614328261331</v>
+        <v>8.25018600142649</v>
       </c>
       <c r="E17" t="n">
-        <v>2.999102253718824</v>
+        <v>2.872313701778845</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8871891952017288</v>
+        <v>0.9073362588875256</v>
       </c>
       <c r="G17" t="n">
-        <v>0.942546204770166</v>
+        <v>0.9530612281974565</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9465261146144828</v>
+        <v>0.9559435981540918</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8042073316205011</v>
+        <v>0.8242704083692285</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0119100733175736</v>
+        <v>3.373345379707603</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1261183647487651</v>
+        <v>3.408069245505356</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4713663449348319</v>
+        <v>13.62516741619089</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4727102382561211</v>
+        <v>3.691228442699109</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3952166070038038</v>
+        <v>0.8536196526284346</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1227343768284408</v>
+        <v>0.9545176164728159</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1628274912733867</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+        <v>0.963245689228162</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8593481108318176</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.257285339310963</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.40912340654384</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6.726769013568754</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.593601552584505</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.9091914560838192</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.9545451700240458</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.9518390584743139</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.8177015366531402</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.204066334762007</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.930870151978912</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.202143364039082</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.683680935588112</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.914272884481388</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.964183925742937</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.9681340033390243</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.8620651736777192</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.01707987373763703</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.2158015003055254</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.008962821077750038</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.008246019057982723</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.017080347256129</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.1913033413154253</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.3239652267103865</v>
+      </c>
+      <c r="AO17" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="AP17" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S17" t="n">
+      <c r="AQ17" t="n">
         <v>7</v>
       </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="AR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1639,67 +2911,139 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.790300998586384</v>
+        <v>2.555144986620137</v>
       </c>
       <c r="C18" t="n">
-        <v>2.933111427597297</v>
+        <v>2.370064392210778</v>
       </c>
       <c r="D18" t="n">
-        <v>10.28562896302732</v>
+        <v>8.663157758752426</v>
       </c>
       <c r="E18" t="n">
-        <v>3.207121600910592</v>
+        <v>2.94332427006479</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8709972391445702</v>
+        <v>0.9026978776436363</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9347457029899578</v>
+        <v>0.9516249945649002</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9395606460818382</v>
+        <v>0.953396321283697</v>
       </c>
       <c r="I18" t="n">
-        <v>0.789223231659012</v>
+        <v>0.8209886416471214</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01056018580357931</v>
+        <v>3.207568344160459</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1242723623981223</v>
+        <v>3.5487069330904</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4661304301057355</v>
+        <v>12.64888275151362</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4679625858338431</v>
+        <v>3.556526782060501</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3853234959636532</v>
+        <v>0.8641082495009524</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1103863492133157</v>
+        <v>0.9638026644950545</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1814007371104254</v>
-      </c>
-      <c r="Q18" t="inlineStr">
+        <v>0.9647271715391178</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.8636287988060731</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.641860468500553</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.511232052330628</v>
+      </c>
+      <c r="T18" t="n">
+        <v>9.213735602371914</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.035413580119176</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.87561845629122</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.935879334212951</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.9261128072071672</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.7694120758271673</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.266300834329523</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.07174463158119</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>6.886186647826015</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.62415446340836</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9180337174085583</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.9670514700760624</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.9708913212609268</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.867127047148996</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.01611314505377809</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.1874631888767884</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.00861150264533822</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.009995364955322272</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.02049494872091495</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.201821752270704</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.3337919944880194</v>
+      </c>
+      <c r="AO18" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="AQ18" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1708,67 +3052,139 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.749322867903916</v>
+        <v>2.57697049556653</v>
       </c>
       <c r="C19" t="n">
-        <v>2.748882947362103</v>
+        <v>2.43213655457671</v>
       </c>
       <c r="D19" t="n">
-        <v>10.06209318149188</v>
+        <v>8.782534617908839</v>
       </c>
       <c r="E19" t="n">
-        <v>3.172080260884311</v>
+        <v>2.96353414319944</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8738008336619016</v>
+        <v>0.9013570707370069</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9358473014525082</v>
+        <v>0.9508181976140438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9419779865398977</v>
+        <v>0.9537500972033409</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7928839905266899</v>
+        <v>0.8205510727508405</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01167603191286409</v>
+        <v>3.285332127720497</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1171868412578154</v>
+        <v>3.595560735044413</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4674576334237451</v>
+        <v>13.03645297119027</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4689406813746118</v>
+        <v>3.610602854259974</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3872187022066856</v>
+        <v>0.8599444354607868</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1239883258601182</v>
+        <v>0.9583597360603727</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1769940181138654</v>
-      </c>
-      <c r="Q19" t="inlineStr">
+        <v>0.9599299907226895</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8529270788704342</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.634218757869413</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.552786641690815</v>
+      </c>
+      <c r="T19" t="n">
+        <v>9.049025547703785</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.008159827486529</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.8778419725443569</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.9371094513055387</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.9325282508188992</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.78228926538076</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.285319365809653</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.099404364844164</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7.077082101465705</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.660278575913753</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9157614887428726</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.9655479022751257</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.969056500847951</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.8612215280991732</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.01306452280539055</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.1395447095885805</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.00693093712481635</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.0074839125532557</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.01601520942612983</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.1236941386339765</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.1883294051860576</v>
+      </c>
+      <c r="AO19" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="AP19" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="AQ19" t="n">
         <v>3</v>
       </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1777,67 +3193,139 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.66822229896156</v>
+        <v>2.581066444707868</v>
       </c>
       <c r="C20" t="n">
-        <v>2.738719492754972</v>
+        <v>2.567712772834254</v>
       </c>
       <c r="D20" t="n">
-        <v>9.65229732070812</v>
+        <v>8.840149928523267</v>
       </c>
       <c r="E20" t="n">
-        <v>3.106814658248561</v>
+        <v>2.973238962566458</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8789405093801547</v>
+        <v>0.9007099519658704</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9382728402628296</v>
+        <v>0.9501505884240747</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9455774697548819</v>
+        <v>0.9544080121151276</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8007057361818527</v>
+        <v>0.8208427853483611</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01069174723570904</v>
+        <v>3.379117825920258</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1258490813351283</v>
+        <v>3.553636685394379</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4687496001447075</v>
+        <v>13.65279630698507</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4709108177332016</v>
+        <v>3.694969053589634</v>
       </c>
       <c r="N20" t="n">
-        <v>0.390776625602931</v>
+        <v>0.8533228249632466</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1056346855121462</v>
+        <v>0.94909834208598</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1657034104062907</v>
-      </c>
-      <c r="Q20" t="inlineStr">
+        <v>0.9519582049542125</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.8379446709605394</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.669374798677091</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.665951853647768</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9.156315654281977</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.025940457821663</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.8763936013671506</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.936440556324633</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.9349783699871989</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.7847037384220586</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.238318822731593</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.048942393763658</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.901965028465857</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.627159117462408</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9178459073371061</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.9658682048262163</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.9681340033390243</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.8586905913635348</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.01377453536040368</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.1620105997771155</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.007623383508960857</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.008614487238287227</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.01820203459165237</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.169712576691234</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.2771886375820531</v>
+      </c>
+      <c r="AO20" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="AP20" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="AQ20" t="n">
         <v>4</v>
       </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1846,67 +3334,139 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.661024540925587</v>
+        <v>2.459379348016043</v>
       </c>
       <c r="C21" t="n">
-        <v>2.712847751219675</v>
+        <v>2.305268627955275</v>
       </c>
       <c r="D21" t="n">
-        <v>10.08691142244051</v>
+        <v>8.243768024733317</v>
       </c>
       <c r="E21" t="n">
-        <v>3.175989833491365</v>
+        <v>2.87119627067418</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8734895623129683</v>
+        <v>0.9074083437751462</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9349042643118369</v>
+        <v>0.9531498182049287</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9430143545215396</v>
+        <v>0.9578618397796097</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7970336084978155</v>
+        <v>0.8272604624938149</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01414535125664057</v>
+        <v>3.173230912516752</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1757869063558088</v>
+        <v>3.235436194524603</v>
       </c>
       <c r="L21" t="n">
-        <v>0.470247760924802</v>
+        <v>12.6983806238736</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4722097738905301</v>
+        <v>3.563478725048545</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3940019215363327</v>
+        <v>0.8635764750625996</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1531159328648928</v>
+        <v>0.9459800693928855</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1841915449000608</v>
-      </c>
-      <c r="Q21" t="inlineStr">
+        <v>0.950970550080242</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.8293832950120282</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.627424999897716</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.688540510161131</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8.691893604681297</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.948201757797674</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.8826631031148302</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.9400456543077005</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.9352040388579635</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.7879230358104569</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.09980285402008</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.954443158568139</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.357255660118217</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.521359883102414</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9243295831797126</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.9664467176679291</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.9700298713812673</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.862346388870568</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.01234120252264892</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.1746194157263248</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.006711869943403392</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.007255296078217344</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.01629736809358051</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.170203877758093</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.2756150738090908</v>
+      </c>
+      <c r="AO21" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="AP21" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="AQ21" t="n">
         <v>7</v>
       </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="AR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1915,67 +3475,139 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5012378676864498</v>
+        <v>0.5132442749029524</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3539505796001851</v>
+        <v>0.3501987967180182</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4854717180408585</v>
+        <v>0.5185989586266314</v>
       </c>
       <c r="E22" t="n">
-        <v>0.696758005365463</v>
+        <v>0.7201381524587011</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9134200301618874</v>
+        <v>0.9172596681708314</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9558002896476666</v>
+        <v>0.9578275600148701</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9672408951938515</v>
+        <v>0.9665646207135652</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8482098337360962</v>
+        <v>0.849435501644495</v>
       </c>
       <c r="J22" t="n">
-        <v>0.01537126264575589</v>
+        <v>0.4126556192937063</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06622489516352065</v>
+        <v>0.3358516054362966</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4812528271102364</v>
+        <v>0.2667568305354022</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4822746276707122</v>
+        <v>0.5164850729066641</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4212762530601726</v>
+        <v>0.9521483323604545</v>
       </c>
       <c r="O22" t="n">
-        <v>0.03876901275709077</v>
+        <v>0.9897913437144799</v>
       </c>
       <c r="P22" t="n">
-        <v>0.02903638701859923</v>
-      </c>
-      <c r="Q22" t="inlineStr">
+        <v>0.9897779959256127</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.9289548600082173</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3989664819566399</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2986187951010488</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.3271380005420068</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.5719597892701958</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.8893594016813257</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.9690848382952385</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.9720052417108995</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.8670469814819192</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.6178219768776745</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.4642169389134284</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.7241050959663593</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.8509436502885248</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8959269698541612</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.9574973957851581</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.9648713352187653</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.8487778494379815</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.0207590447732473</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.102790201411136</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.01093614007720645</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.01049462106767163</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.02340166640528218</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.06641039925930531</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.06988214064931658</v>
+      </c>
+      <c r="AO22" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="AP22" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S22" t="n">
+      <c r="AQ22" t="n">
         <v>2</v>
       </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="AR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1984,67 +3616,139 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.5008868119560096</v>
+        <v>0.5157484841901672</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3533361236123733</v>
+        <v>0.3714139105360612</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5031727393270998</v>
+        <v>0.5409849461497325</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7093466989611638</v>
+        <v>0.7355167884893807</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9102631956190819</v>
+        <v>0.913688075892879</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9541920690452055</v>
+        <v>0.9560113053824792</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9664951084154361</v>
+        <v>0.9648196091315663</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8463823510462675</v>
+        <v>0.8455576205024397</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01352787871626787</v>
+        <v>0.338290938184044</v>
       </c>
       <c r="K23" t="n">
-        <v>0.05597160970868714</v>
+        <v>0.2626687381584067</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4798595300149763</v>
+        <v>0.173911599059272</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4814272772565177</v>
+        <v>0.4170270963130238</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4189673282801969</v>
+        <v>0.9688031979531946</v>
       </c>
       <c r="O23" t="n">
-        <v>0.03678412903569844</v>
+        <v>0.9905192108357428</v>
       </c>
       <c r="P23" t="n">
-        <v>0.03417189872319853</v>
-      </c>
-      <c r="Q23" t="inlineStr">
+        <v>0.9885090497769902</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.9204712539807449</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.4453137561685552</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.3236367190509567</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.3800389945066152</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.6164730282069243</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.8714678769602613</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.9610055575857298</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.9650225841331437</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.8520978955942999</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.622190074618477</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.4526406008322894</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.7702356551603498</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.8776307054566572</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8892967899198059</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.952455296370105</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.9595250368470754</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.8421456930367082</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.02308759880216504</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.1078914411409481</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.01179451318662866</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.01117363999786664</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.02278260089575762</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.07199673698375539</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.07037640443165114</v>
+      </c>
+      <c r="AO23" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="AP23" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="AQ23" t="n">
         <v>3</v>
       </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2053,67 +3757,139 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.491403883638923</v>
+        <v>0.5087651766748822</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3454736716079901</v>
+        <v>0.3621327076669624</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4972503021034655</v>
+        <v>0.5394795472960044</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7051597706218539</v>
+        <v>0.7344927142565844</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9113194145853682</v>
+        <v>0.9139282560911243</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9547532929984951</v>
+        <v>0.9561256438670105</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9672589085539622</v>
+        <v>0.9652831419238906</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8482995261380509</v>
+        <v>0.8469220601635332</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01388673527165901</v>
+        <v>0.2989635895677221</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05617288063452963</v>
+        <v>0.2281346197397995</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4803241129239936</v>
+        <v>0.1536174270201261</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4817383949075195</v>
+        <v>0.3919405911871416</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4199341187543066</v>
+        <v>0.97244362947837</v>
       </c>
       <c r="O24" t="n">
-        <v>0.03260405555528512</v>
+        <v>0.9882543395158241</v>
       </c>
       <c r="P24" t="n">
-        <v>0.03359136224275411</v>
-      </c>
-      <c r="Q24" t="inlineStr">
+        <v>0.987804079694422</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.9141085494601408</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.4617958515126805</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3491228579526154</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.4041291902228472</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.6357115621277052</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.8633203867168721</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.9578903378414887</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.964926049696585</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.8568186595588112</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.6130053522483825</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.4320702154146989</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.7603321010266324</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.8719702409065532</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8907201922596746</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.9515617476598611</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.9587457918372599</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.8404876539363897</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.02255321508165986</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.1030952026988996</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.01152974566478454</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.01194687690520929</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.02194425036269515</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.06002651797016481</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.05408965189384962</v>
+      </c>
+      <c r="AO24" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="AQ24" t="n">
         <v>4</v>
       </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2122,67 +3898,139 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5361741445595248</v>
+        <v>0.554007859950745</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3493248494540024</v>
+        <v>0.35830661515927</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6206910806613045</v>
+        <v>0.6804716247374922</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7878395018411456</v>
+        <v>0.8249070400581463</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8893047461975563</v>
+        <v>0.8914335497699121</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9434284069956681</v>
+        <v>0.9446585131581614</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9592043271724954</v>
+        <v>0.9572804376455137</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8318858165803263</v>
+        <v>0.8304769716166684</v>
       </c>
       <c r="J25" t="n">
-        <v>0.02109380638398284</v>
+        <v>0.4009277915835567</v>
       </c>
       <c r="K25" t="n">
-        <v>0.07646598663589205</v>
+        <v>0.3167314069457239</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4763307373945045</v>
+        <v>0.243860816038509</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4784368553001128</v>
+        <v>0.4938226564653641</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4139377209346621</v>
+        <v>0.9562554904556252</v>
       </c>
       <c r="O25" t="n">
-        <v>0.04529918775139621</v>
+        <v>0.9791940451952009</v>
       </c>
       <c r="P25" t="n">
-        <v>0.02833110886502463</v>
-      </c>
-      <c r="Q25" t="inlineStr">
+        <v>0.9777935045219549</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.8738114208296472</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.4814476271138583</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2998700220763002</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5069057859537338</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.7119731637876064</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.8285605482817721</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.9327858355855005</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.9458444094034555</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.824560105801317</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.6528496762516718</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.4307023273096822</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.9425180377555573</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.9708336818196809</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8645352605543767</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.9385982748962007</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.9483377889235517</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.8208675245826222</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.0333028619731493</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.1305019643407068</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.01699890735188042</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.01447859018526321</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.02832073942760355</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.07504645817387301</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.05591487819009691</v>
+      </c>
+      <c r="AO25" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="AP25" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S25" t="n">
+      <c r="AQ25" t="n">
         <v>7</v>
       </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2191,67 +4039,139 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.77512043816795</v>
+        <v>0.7902117320089761</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6388779258934005</v>
+        <v>0.6574858949055227</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9409047695139775</v>
+        <v>0.9800566646763724</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9700024585092439</v>
+        <v>0.9899781132309807</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8321972145075602</v>
+        <v>0.8436359882760722</v>
       </c>
       <c r="G26" t="n">
-        <v>0.913268937159606</v>
+        <v>0.919537806697898</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9297238920924896</v>
+        <v>0.9300303007084264</v>
       </c>
       <c r="I26" t="n">
-        <v>0.775446872650282</v>
+        <v>0.7794900158600137</v>
       </c>
       <c r="J26" t="n">
-        <v>0.01910850620260529</v>
+        <v>0.5924437175494752</v>
       </c>
       <c r="K26" t="n">
-        <v>0.04828181966667922</v>
+        <v>0.6200319887872494</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4595237088378046</v>
+        <v>0.4903028144778309</v>
       </c>
       <c r="M26" t="n">
-        <v>0.461257273520101</v>
+        <v>0.700216262648784</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3786073623412491</v>
+        <v>0.9120479604063477</v>
       </c>
       <c r="O26" t="n">
-        <v>0.04101596493361631</v>
+        <v>0.9840048617923169</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0433374743184331</v>
-      </c>
-      <c r="Q26" t="inlineStr">
+        <v>0.9793444387036049</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.8886577313777237</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.6573781658910208</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.5761818451393643</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.5833704086347977</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.7637868869225222</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.802699622343398</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.9895433712183214</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.9890596588362934</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.9103206511566067</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.9411688344611314</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.8509729242304156</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.394193688178267</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.180759792751374</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.7996175381899868</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.9456924948402657</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.954849566788183</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.8338554975351162</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.02389101315204328</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.08484503661234505</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.01302020313695351</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.01836252231625513</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.028230229970446</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.07534596756777701</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.07072639631399402</v>
+      </c>
+      <c r="AO26" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="AP26" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S26" t="n">
+      <c r="AQ26" t="n">
         <v>2</v>
       </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2260,67 +4180,139 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.7747313258873919</v>
+        <v>0.7902936350569257</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6402422777076994</v>
+        <v>0.653305105373593</v>
       </c>
       <c r="D27" t="n">
-        <v>0.939323199859571</v>
+        <v>0.9784160605447565</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9691868756125266</v>
+        <v>0.9891491599070165</v>
       </c>
       <c r="F27" t="n">
-        <v>0.832479274713926</v>
+        <v>0.8438977399205601</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9131717963902399</v>
+        <v>0.9194019159238057</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9299355631028872</v>
+        <v>0.929780498016843</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7758617000093228</v>
+        <v>0.7791309527913048</v>
       </c>
       <c r="J27" t="n">
-        <v>0.01870761073491206</v>
+        <v>0.595056785764719</v>
       </c>
       <c r="K27" t="n">
-        <v>0.05226524752675932</v>
+        <v>0.6356227957840801</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4597854378112921</v>
+        <v>0.4950643794390819</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4619767645212061</v>
+        <v>0.7036081149610782</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3801106984196344</v>
+        <v>0.9111938161150372</v>
       </c>
       <c r="O27" t="n">
-        <v>0.04156579380300052</v>
+        <v>0.9839093479320323</v>
       </c>
       <c r="P27" t="n">
-        <v>0.03368811921404696</v>
-      </c>
-      <c r="Q27" t="inlineStr">
+        <v>0.9793444387036049</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.8886577313777237</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.6718808862355918</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.5949339814343891</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.6040711607799114</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.7772201494942803</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.7956984680929371</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.9892609612322988</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.9892205495638916</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.9134678271329476</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.9317493316188524</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.7559782951424219</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.376930992377141</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.173427028995472</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8020986435854838</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.9446275446903731</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.952457623410228</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.8283287005340549</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.02803296536265276</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.08272679040409558</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.01481944659106238</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.02226106527827626</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.03338107190181305</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0.06720370162249517</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.0652668460340633</v>
+      </c>
+      <c r="AO27" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="AP27" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S27" t="n">
+      <c r="AQ27" t="n">
         <v>3</v>
       </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2329,67 +4321,139 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7551778068053583</v>
+        <v>0.7711680468415784</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6227983548410425</v>
+        <v>0.6441629782801455</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9056890561305176</v>
+        <v>0.94325236715105</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9516769704739722</v>
+        <v>0.9712118034450827</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8384776532834209</v>
+        <v>0.8495079626395554</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9165042450540296</v>
+        <v>0.922395189072143</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9324928990747419</v>
+        <v>0.9320620893876223</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7799427042982653</v>
+        <v>0.7827215834783932</v>
       </c>
       <c r="J28" t="n">
-        <v>0.01745058460163285</v>
+        <v>0.5638097436786278</v>
       </c>
       <c r="K28" t="n">
-        <v>0.05029467096328999</v>
+        <v>0.581477678710259</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4600263493169767</v>
+        <v>0.4277399461966401</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4622536106420287</v>
+        <v>0.6540183072335515</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3810012996980442</v>
+        <v>0.9232706817648206</v>
       </c>
       <c r="O28" t="n">
-        <v>0.03830367407357088</v>
+        <v>0.9858262256593239</v>
       </c>
       <c r="P28" t="n">
-        <v>0.03461288368198601</v>
-      </c>
-      <c r="Q28" t="inlineStr">
+        <v>0.9797674207531457</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.89289953439146</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.6651834440216952</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.5961368715192957</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.5931206699135473</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.7701432788212511</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.7994020086762088</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.9888774115097266</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.9892849058549308</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.9142546211270328</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.9096362843804334</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.7436384335416797</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.339054257424557</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.157175119601418</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8075425309445218</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.9445650159333702</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.9526473526300091</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.8277760208339489</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.02822898915187427</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.08050353554754069</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.01466630726557394</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.02376895363513637</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.03171639842034862</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.07108194970994519</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.07157406452658033</v>
+      </c>
+      <c r="AO28" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="AP28" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S28" t="n">
+      <c r="AQ28" t="n">
         <v>4</v>
       </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2398,67 +4462,139 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.7371720244660682</v>
+        <v>0.7564399195152284</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6132378763707744</v>
+        <v>0.6332106426162127</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8787109177528089</v>
+        <v>0.9207396281570147</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9373958170126475</v>
+        <v>0.9595517850314358</v>
       </c>
       <c r="F29" t="n">
-        <v>0.84328898692085</v>
+        <v>0.8530997775936056</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9210133068748307</v>
+        <v>0.924199008368894</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9346208324560447</v>
+        <v>0.9338612098558847</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7807499359158583</v>
+        <v>0.7848759618906462</v>
       </c>
       <c r="J29" t="n">
-        <v>0.02301229038118435</v>
+        <v>0.5474933583320598</v>
       </c>
       <c r="K29" t="n">
-        <v>0.06448190594666653</v>
+        <v>0.5704005385632097</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4604328657794787</v>
+        <v>0.394729492716197</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4628373749081081</v>
+        <v>0.6282750136016846</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3806423421455101</v>
+        <v>0.9291921992959986</v>
       </c>
       <c r="O29" t="n">
-        <v>0.04827067268661039</v>
+        <v>0.9867499063192157</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0325675257918171</v>
-      </c>
-      <c r="Q29" t="inlineStr">
+        <v>0.980754378868741</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.895020435898328</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.6476234461663144</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.5784259831918669</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.5760440843431359</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.7589756809958643</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.8051774418011287</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.9871503007992791</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.9869359012319991</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.9048130931980102</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.8971707854092882</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.6791991269662891</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.317124133231355</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.147660286509625</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8106944690940733</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.9416395184608123</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.9498352945511099</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.8222492238328876</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.02901457712849803</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.09928622746408849</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.01440068826500945</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.02166922108031366</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.03364540438769531</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.08500998218634687</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.05751243562264913</v>
+      </c>
+      <c r="AO29" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="AP29" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S29" t="n">
+      <c r="AQ29" t="n">
         <v>7</v>
       </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2467,67 +4603,139 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.4202146556928675</v>
+        <v>0.3842514670764387</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3034553396899603</v>
+        <v>0.2850928009836506</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3163391133681292</v>
+        <v>0.2770003325866687</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5624403198279166</v>
+        <v>0.5263082106396106</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9435834676331798</v>
+        <v>0.9558057357158871</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9718939670303605</v>
+        <v>0.9785313091927424</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9790931810992202</v>
+        <v>0.982552894789669</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8751960351742401</v>
+        <v>0.888357938292533</v>
       </c>
       <c r="J30" t="n">
-        <v>0.006999056066933573</v>
+        <v>0.2998531436633171</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03303790390094208</v>
+        <v>0.2090674126270258</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4874608103106244</v>
+        <v>0.1665048085317806</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4878530569441755</v>
+        <v>0.4080500073909821</v>
       </c>
       <c r="N30" t="n">
-        <v>0.4327743791420872</v>
+        <v>0.9701318510110596</v>
       </c>
       <c r="O30" t="n">
-        <v>0.02873019722820683</v>
+        <v>0.9920342231025692</v>
       </c>
       <c r="P30" t="n">
-        <v>0.03709858805378433</v>
-      </c>
-      <c r="Q30" t="inlineStr">
+        <v>0.9869581155953402</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.9204712539807449</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.2511229706246023</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.1897118698502541</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.1288551017956565</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.3589639282653014</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.9564202094056191</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.9841238494955623</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.9839111555531557</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.8985187412453284</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.494158723065774</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.4267522539283037</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.4053330571764865</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.6366577237232629</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.941742932464332</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.9805684014539912</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.9856805650026181</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.9048748389987533</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.008922563711848297</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.05308258487571144</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.004452331392380604</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.006019775682244766</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.01446371921941064</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.04440941026225395</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.05088733266989169</v>
+      </c>
+      <c r="AO30" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="AP30" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S30" t="n">
+      <c r="AQ30" t="n">
         <v>2</v>
       </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2536,67 +4744,139 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.4081450684029578</v>
+        <v>0.3793902745631374</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2949675360688062</v>
+        <v>0.287209885669659</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2973890597874504</v>
+        <v>0.2742573052945485</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5453338975228391</v>
+        <v>0.5236958137072976</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9469630570232</v>
+        <v>0.9562433744434456</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9732656758644955</v>
+        <v>0.9788616412744237</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9809935064163203</v>
+        <v>0.982814421073276</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8812054261052101</v>
+        <v>0.8902250662498189</v>
       </c>
       <c r="J31" t="n">
-        <v>0.006986267458265638</v>
+        <v>0.3053593050615875</v>
       </c>
       <c r="K31" t="n">
-        <v>0.03807572042740165</v>
+        <v>0.2669382534644993</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4881643577598822</v>
+        <v>0.1471540665933453</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4884971897190937</v>
+        <v>0.383606656085821</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4340452261306532</v>
+        <v>0.9736030471186087</v>
       </c>
       <c r="O31" t="n">
-        <v>0.02967453270289114</v>
+        <v>0.9934210751160382</v>
       </c>
       <c r="P31" t="n">
-        <v>0.03289751099832539</v>
-      </c>
-      <c r="Q31" t="inlineStr">
+        <v>0.9920339001898306</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.9416802690494257</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.2334212846668663</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.1709511807291917</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.1129139433688606</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.3360267003808783</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.9618116323014957</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.9868643993796259</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.9875151078513522</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.9142546211270328</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.493168207873879</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.3752770730498565</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.4164826322491143</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.6453546561768299</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9401404440008332</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.9802023302984311</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.9848471116442938</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.9012824209480634</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.009074152674177771</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.05758111308620328</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.004309112806135051</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.004973689140805482</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.01638769494576781</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.04126025564174926</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.05275905149098548</v>
+      </c>
+      <c r="AO31" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="AP31" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S31" t="n">
+      <c r="AQ31" t="n">
         <v>3</v>
       </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2605,67 +4885,139 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.4047382816651189</v>
+        <v>0.3722270766706862</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2743683739259483</v>
+        <v>0.3078952856527111</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3037679782059547</v>
+        <v>0.2607789091009857</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5511515020445419</v>
+        <v>0.5106651633908326</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9458254283133286</v>
+        <v>0.9583937971448983</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9730306895010441</v>
+        <v>0.9799019469554824</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9810787472076231</v>
+        <v>0.9835593200741707</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8816314650144954</v>
+        <v>0.8920921942071048</v>
       </c>
       <c r="J32" t="n">
-        <v>0.006697629723066312</v>
+        <v>0.2731184764227473</v>
       </c>
       <c r="K32" t="n">
-        <v>0.03539005017695723</v>
+        <v>0.2589584697557306</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4877791799082793</v>
+        <v>0.1061802545739805</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4882136981802945</v>
+        <v>0.3258531180976798</v>
       </c>
       <c r="N32" t="n">
-        <v>0.4340464866136703</v>
+        <v>0.9809530566038041</v>
       </c>
       <c r="O32" t="n">
-        <v>0.02974827640848904</v>
+        <v>0.9956049544330675</v>
       </c>
       <c r="P32" t="n">
-        <v>0.02044702825445227</v>
-      </c>
-      <c r="Q32" t="inlineStr">
+        <v>0.9955587506026712</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.9544056780906341</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.2327055790582205</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.1691268532299821</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.1043159325256045</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.3229797710780112</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.9647195459723997</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.9861268606157797</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.9862279820305676</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.9040262992039249</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.4912876241004948</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.4085326804265534</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.4100985381308673</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.6403893644735735</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.941058006966932</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.9788646323898079</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.982224782785176</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.89465026454679</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.009360143361477002</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.05732598578010453</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.004582228098969798</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.005950185567279664</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.01801621835580175</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.04117124487041407</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.05142335335154541</v>
+      </c>
+      <c r="AO32" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="AP32" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S32" t="n">
+      <c r="AQ32" t="n">
         <v>4</v>
       </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2674,67 +5026,139 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3578022245302815</v>
+        <v>0.3589193569722405</v>
       </c>
       <c r="C33" t="n">
-        <v>0.25315950408095</v>
+        <v>0.27551104320986</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2364717804127856</v>
+        <v>0.247023168611303</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4862836419341963</v>
+        <v>0.4970142539317188</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9578271630357247</v>
+        <v>0.9605884689886026</v>
       </c>
       <c r="G33" t="n">
-        <v>0.97919579784766</v>
+        <v>0.9808199285816487</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9846191300405975</v>
+        <v>0.9830010967308853</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8942220359388974</v>
+        <v>0.891733131138396</v>
       </c>
       <c r="J33" t="n">
-        <v>0.005084336531834543</v>
+        <v>0.2060860377254519</v>
       </c>
       <c r="K33" t="n">
-        <v>0.03029284958176953</v>
+        <v>0.1249226816939575</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4905958912372626</v>
+        <v>0.07376256696626998</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4908610793679509</v>
+        <v>0.2715926489547719</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4418159638773577</v>
+        <v>0.9867682419541972</v>
       </c>
       <c r="O33" t="n">
-        <v>0.02355612201147592</v>
+        <v>0.9945026434045054</v>
       </c>
       <c r="P33" t="n">
-        <v>0.02596962344937276</v>
-      </c>
-      <c r="Q33" t="inlineStr">
+        <v>0.9916109181402898</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.9395593675425576</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.2647848159357122</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.2023519533729914</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.1392797918002602</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.3732020790406455</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.9528944987346328</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.9828301296102075</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.9799210655087238</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.8780620973991125</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.4705090511994202</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.3480148375753538</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.3741387851631752</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.6116688525363828</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9462263733760221</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.9793096868321072</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.9817436836921596</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.8927158855964186</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.008748610985937211</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.05008306652151534</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.004292928046703171</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.005772265892174944</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.01732263983749405</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.04213209508328969</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.05315800227306794</v>
+      </c>
+      <c r="AO33" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="AP33" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="AQ33" t="n">
         <v>7</v>
       </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2743,67 +5167,139 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.3868254759102751</v>
+        <v>0.3865904548160095</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2538449441745734</v>
+        <v>0.2641813603023027</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2850986498621596</v>
+        <v>0.3001846814694351</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5339462986688451</v>
+        <v>0.5478911219114936</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9491549526189393</v>
+        <v>0.9521067681651552</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9748947824630414</v>
+        <v>0.9766316354468949</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9813707768836859</v>
+        <v>0.9803001614915637</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8831226011969936</v>
+        <v>0.8813921147595815</v>
       </c>
       <c r="J34" t="n">
-        <v>0.007498658770924316</v>
+        <v>0.2124282999671183</v>
       </c>
       <c r="K34" t="n">
-        <v>0.03920650428177952</v>
+        <v>0.1981368184235565</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4882146456890368</v>
+        <v>0.06861925420986464</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4888738391596734</v>
+        <v>0.2619527709528278</v>
       </c>
       <c r="N34" t="n">
-        <v>0.437026968734419</v>
+        <v>0.9876908653490387</v>
       </c>
       <c r="O34" t="n">
-        <v>0.02686073962729757</v>
+        <v>0.9969022288791917</v>
       </c>
       <c r="P34" t="n">
-        <v>0.02481631439693663</v>
-      </c>
-      <c r="Q34" t="inlineStr">
+        <v>0.9945717924870758</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.952284776583766</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.2930428382491294</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.2422378199042217</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.164714987341216</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.4058509422697156</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.9442921191628886</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.9823996147298959</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.9801784906728808</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.8835696553577089</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.5055868449496177</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.3779056734021937</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.4650003573095416</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.6819093468413097</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9331671652724427</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.9758175346620218</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.9806527406784179</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.881938631444349</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.01230117775823969</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.07347918165992268</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.005389439604782331</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.006340177030639493</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.01790749850561635</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.0537714071526052</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.04534251559695089</v>
+      </c>
+      <c r="AO34" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="AP34" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="AQ34" t="n">
         <v>2</v>
       </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2812,67 +5308,139 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.3949808277337397</v>
+        <v>0.380151110929298</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2698208718025505</v>
+        <v>0.2447361472657157</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2949602451765442</v>
+        <v>0.2955077561718726</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5431024260455335</v>
+        <v>0.5436062510419399</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9473962165419527</v>
+        <v>0.9528529523690058</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9765647308159221</v>
+        <v>0.9767282862688436</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9821619618188911</v>
+        <v>0.9812551833341151</v>
       </c>
       <c r="I35" t="n">
-        <v>0.886553335571764</v>
+        <v>0.8852699959016369</v>
       </c>
       <c r="J35" t="n">
-        <v>0.008113117663299196</v>
+        <v>0.2156369981866703</v>
       </c>
       <c r="K35" t="n">
-        <v>0.03914404554015488</v>
+        <v>0.1694690469146076</v>
       </c>
       <c r="L35" t="n">
-        <v>0.4882277932428282</v>
+        <v>0.07606394276686591</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4887776187821816</v>
+        <v>0.2757969230554719</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4346812098396106</v>
+        <v>0.986355414025095</v>
       </c>
       <c r="O35" t="n">
-        <v>0.02575466996606615</v>
+        <v>0.9955702944078205</v>
       </c>
       <c r="P35" t="n">
-        <v>0.02426273888755812</v>
-      </c>
-      <c r="Q35" t="inlineStr">
+        <v>0.9954177565861575</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.9544056780906341</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.2845413543336299</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.1947103902731258</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.1617170010354142</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.4021405239905749</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.9453060612854043</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.9831333175936383</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.9839111555531557</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.8945847712749021</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.4968661806447006</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.3689357424056565</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.4549165343507594</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.6744750064685565</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9346164770044283</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.9746875809205457</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.9809441105516532</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.885807389345092</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.01001800426126565</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.06434021596899528</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.004941503781554779</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.006829749877579894</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.01680471620489565</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.04555830949247661</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.06088223434454494</v>
+      </c>
+      <c r="AO35" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="AP35" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="AQ35" t="n">
         <v>3</v>
       </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="n">
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2881,67 +5449,139 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.3645404962168399</v>
+        <v>0.3837835899882285</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2579573583276449</v>
+        <v>0.2555410460732435</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2435305568141568</v>
+        <v>0.2846092128133036</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4934881526583559</v>
+        <v>0.5334877813158457</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9565682871317049</v>
+        <v>0.9545917701567056</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9783673475566147</v>
+        <v>0.9779514445453874</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9841383809562722</v>
+        <v>0.9817367524218605</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8917330717846523</v>
+        <v>0.884623682377961</v>
       </c>
       <c r="J36" t="n">
-        <v>0.005924109944944689</v>
+        <v>0.2965659536065395</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03327883164529119</v>
+        <v>0.2191381269221404</v>
       </c>
       <c r="L36" t="n">
-        <v>0.489966333502983</v>
+        <v>0.1493209170613373</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4904196872548738</v>
+        <v>0.3864206478196233</v>
       </c>
       <c r="N36" t="n">
-        <v>0.4404659865660521</v>
+        <v>0.9732143507609152</v>
       </c>
       <c r="O36" t="n">
-        <v>0.02346056938923546</v>
+        <v>0.9902704514165598</v>
       </c>
       <c r="P36" t="n">
-        <v>0.02529122990607635</v>
-      </c>
-      <c r="Q36" t="inlineStr">
+        <v>0.9887910378100174</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.9289548600082173</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.269489733573688</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.1949464304460657</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.1431292618080793</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.3783242812827102</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.9515925782479598</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.9834640511657106</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.9814334383481456</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.8851432433458795</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.483508661580305</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.4062071843772981</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.4179913738501851</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.6465225238537209</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9399235979780594</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.9791928570957641</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.9855247160006551</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.8990717021476391</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.009615183106116421</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.06083767156708805</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.004333553317357186</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.005926155055482718</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.01616008913652472</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0.04655579088937103</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0.05531760397607613</v>
+      </c>
+      <c r="AO36" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="AP36" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S36" t="n">
+      <c r="AQ36" t="n">
         <v>4</v>
       </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="n">
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2950,67 +5590,139 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3647649121375232</v>
+        <v>0.3523531711325154</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2328002186808724</v>
+        <v>0.2558327586195088</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2579874698658938</v>
+        <v>0.236961024396177</v>
       </c>
       <c r="E37" t="n">
-        <v>0.507924669479534</v>
+        <v>0.4867864258544778</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9539900131572234</v>
+        <v>0.9621938427314988</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9772364224522676</v>
+        <v>0.9811067625224034</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9840776069095435</v>
+        <v>0.9850139472998887</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8913855137270775</v>
+        <v>0.8954673870529679</v>
       </c>
       <c r="J37" t="n">
-        <v>0.006174512972081214</v>
+        <v>0.2358611312125886</v>
       </c>
       <c r="K37" t="n">
-        <v>0.03534095925440944</v>
+        <v>0.1761129866864128</v>
       </c>
       <c r="L37" t="n">
-        <v>0.4897608839873159</v>
+        <v>0.09809573343764035</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4902613012859114</v>
+        <v>0.3132023841506325</v>
       </c>
       <c r="N37" t="n">
-        <v>0.440832086855683</v>
+        <v>0.9824032830803466</v>
       </c>
       <c r="O37" t="n">
-        <v>0.02699557076003337</v>
+        <v>0.9929295969873344</v>
       </c>
       <c r="P37" t="n">
-        <v>0.02642619888423466</v>
-      </c>
-      <c r="Q37" t="inlineStr">
+        <v>0.9914699241237762</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.9331966630219534</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.2864318699178353</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.2235316078752874</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.1502219839994389</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.3875848087831086</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.949193764824695</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.9797287382428225</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.978923542997616</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.8741281274286862</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.4339398111650255</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.3265726277632321</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.3390708071295717</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.582297868044845</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9512665681700861</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.9788997025451465</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.9839187936760789</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.8990717021476391</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.008902850442876864</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.05009917048454984</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.004269608928856139</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.004560430094566081</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.0143617778148637</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.03908287857122913</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.04098026456635237</v>
+      </c>
+      <c r="AO37" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="AP37" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S37" t="n">
+      <c r="AQ37" t="n">
         <v>7</v>
       </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="n">
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3019,67 +5731,139 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.5334736657190914</v>
+        <v>0.5493583421930488</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4644887057015376</v>
+        <v>0.4825501296653059</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4238746568829184</v>
+        <v>0.4619161543275412</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6510565696488427</v>
+        <v>0.6796441380071936</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9244053697789771</v>
+        <v>0.9263031765672513</v>
       </c>
       <c r="G38" t="n">
-        <v>0.963126590236166</v>
+        <v>0.9638806166382744</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9676201297347493</v>
+        <v>0.9655599990586058</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8492973541097977</v>
+        <v>0.8462039340261155</v>
       </c>
       <c r="J38" t="n">
-        <v>0.007498237235480709</v>
+        <v>0.5935548562860994</v>
       </c>
       <c r="K38" t="n">
-        <v>0.03357782455753244</v>
+        <v>0.5673154403623242</v>
       </c>
       <c r="L38" t="n">
-        <v>0.4829904335951859</v>
+        <v>0.4974105882390185</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4840331635115964</v>
+        <v>0.7052734138183705</v>
       </c>
       <c r="N38" t="n">
-        <v>0.4210796177095062</v>
+        <v>0.9107729459034584</v>
       </c>
       <c r="O38" t="n">
-        <v>0.03003445755963463</v>
+        <v>0.9634971817037008</v>
       </c>
       <c r="P38" t="n">
-        <v>0.02967398991476305</v>
-      </c>
-      <c r="Q38" t="inlineStr">
+        <v>0.9586183182761027</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.865327814802175</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.6519310194720926</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.5999813668311882</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.597840971707298</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.7732017664926135</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.7978055661539705</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.9881757327837771</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.9859062005753715</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.9000923292334987</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.4722519010014341</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.3801756903512015</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.3681282043816945</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.6067356956547838</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9470902526089534</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.9772470013737483</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.9819740691733222</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.8899524870958878</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.01349451466643703</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.0611525957535452</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.006972820347012854</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.01146403129998735</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.01947577444810378</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.05467414805915533</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.06168837342230296</v>
+      </c>
+      <c r="AO38" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="AP38" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S38" t="n">
+      <c r="AQ38" t="n">
         <v>2</v>
       </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="n">
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3088,67 +5872,139 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5310618530985587</v>
+        <v>0.5565391917990669</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4684361148310132</v>
+        <v>0.4800001483710348</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4295099287883289</v>
+        <v>0.4853196861332354</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6553700701041579</v>
+        <v>0.6966488973171747</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9234003644337245</v>
+        <v>0.9225692392822522</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9634380958917876</v>
+        <v>0.9630281790173647</v>
       </c>
       <c r="H39" t="n">
-        <v>0.969080446464223</v>
+        <v>0.9661966802869733</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8527729346855454</v>
+        <v>0.8470656853910167</v>
       </c>
       <c r="J39" t="n">
-        <v>0.007502167212795785</v>
+        <v>0.5509859368247261</v>
       </c>
       <c r="K39" t="n">
-        <v>0.02934721413363062</v>
+        <v>0.4811781277688891</v>
       </c>
       <c r="L39" t="n">
-        <v>0.48348504175847</v>
+        <v>0.4850173086126113</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4841920236522447</v>
+        <v>0.6964318406079746</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4216195246018274</v>
+        <v>0.9129960908420772</v>
       </c>
       <c r="O39" t="n">
-        <v>0.02825005390515883</v>
+        <v>0.9774042895233075</v>
       </c>
       <c r="P39" t="n">
-        <v>0.05240697181073645</v>
-      </c>
-      <c r="Q39" t="inlineStr">
+        <v>0.9727177199274646</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.8865368298708558</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.6475209516822503</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.5803878751442736</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.6140249107629954</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.7835974162559467</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.7923320329743686</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.9841354876576309</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.9826240297323712</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.8922243892926465</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.5044206505369326</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.4092222932361826</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.4088447145428616</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.6394096609708534</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.941238214537351</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.9735990815582088</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.9788367610033698</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.8805569321940839</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.01621023552550904</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.05983121078682874</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.007437817691814119</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.0123443756514785</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.02478805120420158</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.0548543581419848</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.07739440431709443</v>
+      </c>
+      <c r="AO39" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="AP39" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S39" t="n">
+      <c r="AQ39" t="n">
         <v>3</v>
       </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3157,67 +6013,139 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5715063369763871</v>
+        <v>0.605986125634469</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4808056425749809</v>
+        <v>0.4992170065773864</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5205290983026529</v>
+        <v>0.5920397184865179</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7214770254849789</v>
+        <v>0.7694411728563256</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9071678288227067</v>
+        <v>0.9055424968585609</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9541891310467069</v>
+        <v>0.9535807204177927</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9619293950240103</v>
+        <v>0.9573521319198129</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8363928597785539</v>
+        <v>0.8276762796807395</v>
       </c>
       <c r="J40" t="n">
-        <v>0.01214391584304847</v>
+        <v>0.5993300403892641</v>
       </c>
       <c r="K40" t="n">
-        <v>0.04841791750093638</v>
+        <v>0.4651977777656624</v>
       </c>
       <c r="L40" t="n">
-        <v>0.479724550776075</v>
+        <v>0.6375682930090507</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4812075274390388</v>
+        <v>0.7984787367294452</v>
       </c>
       <c r="N40" t="n">
-        <v>0.4153797135062156</v>
+        <v>0.885631022105983</v>
       </c>
       <c r="O40" t="n">
-        <v>0.03628942989728917</v>
+        <v>0.969302047845318</v>
       </c>
       <c r="P40" t="n">
-        <v>0.04049264340539629</v>
-      </c>
-      <c r="Q40" t="inlineStr">
+        <v>0.9635531088540793</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.8547233072678346</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.6680134420945441</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.5925530175632817</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.6509490226017937</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.8068141189901139</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.779844013180087</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.9844815987066922</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.9828492767510085</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.8898640073103908</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.5714977038630936</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.4282912724634409</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.5404304029882424</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.7351397166445589</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9223258751592377</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.9665201387981256</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.9707902092715806</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.859278763739998</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.0175314825124212</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.06857140929712663</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.008206135426644057</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.01212524902294859</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.02244650563206929</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.0581703979727059</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.07992313427501996</v>
+      </c>
+      <c r="AO40" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="AP40" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S40" t="n">
+      <c r="AQ40" t="n">
         <v>4</v>
       </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="n">
+      <c r="AR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3226,67 +6154,139 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.5452711946215545</v>
+        <v>0.5547811925072333</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4493791906655706</v>
+        <v>0.4654627663329407</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4788491642190688</v>
+        <v>0.5078139065179142</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6919892804220805</v>
+        <v>0.7126106275645306</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9146011092831506</v>
+        <v>0.9189803788961928</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9573663567421361</v>
+        <v>0.9592773191525604</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9647560054771462</v>
+        <v>0.9634235998659673</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8418080385465738</v>
+        <v>0.8416079267466423</v>
       </c>
       <c r="J41" t="n">
-        <v>0.007813039305619773</v>
+        <v>0.4102964937107041</v>
       </c>
       <c r="K41" t="n">
-        <v>0.03345405901140036</v>
+        <v>0.3168744682249217</v>
       </c>
       <c r="L41" t="n">
-        <v>0.4803634106588436</v>
+        <v>0.293530563907192</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4815005515121741</v>
+        <v>0.5417846102531817</v>
       </c>
       <c r="N41" t="n">
-        <v>0.4161546304543901</v>
+        <v>0.9473455770262976</v>
       </c>
       <c r="O41" t="n">
-        <v>0.02885219140626338</v>
+        <v>0.9753389183663943</v>
       </c>
       <c r="P41" t="n">
-        <v>0.04386953807831667</v>
-      </c>
-      <c r="Q41" t="inlineStr">
+        <v>0.9720127498448967</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.8822950268571196</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.6252411368635639</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.5475751610297447</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.578280347621864</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.7604474653924911</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.8044211202892695</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.9852199249273627</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.9847156091911459</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.9032395052098396</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.5653945045187334</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.4613820739051331</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.5438046777194629</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.7374311342216729</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9218409027460081</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.9649313602187961</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.9678934506481363</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.8518175877885652</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.01487879967411143</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.06496066060866601</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.008178519688780972</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.01110416491050503</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.02228986184145859</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0.05332206300519055</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0.07514345774974399</v>
+      </c>
+      <c r="AO41" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="AP41" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S41" t="n">
+      <c r="AQ41" t="n">
         <v>7</v>
       </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
+      <c r="AR41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3295,67 +6295,139 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>1.166572297531505</v>
+        <v>1.216508215166781</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9411886989548708</v>
+        <v>1.009872640223081</v>
       </c>
       <c r="D42" t="n">
-        <v>2.515995000550076</v>
+        <v>2.750450826138071</v>
       </c>
       <c r="E42" t="n">
-        <v>1.586188828781137</v>
+        <v>1.658448318802269</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9602703047429294</v>
+        <v>0.9610947667632552</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9800911775547514</v>
+        <v>0.9804989493389238</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9805137636129465</v>
+        <v>0.977375198000519</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8823275396133204</v>
+        <v>0.8768525669593976</v>
       </c>
       <c r="J42" t="n">
-        <v>0.006148201203990344</v>
+        <v>1.311422906940323</v>
       </c>
       <c r="K42" t="n">
-        <v>0.125968432560806</v>
+        <v>0.9915002968498818</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4915212990616157</v>
+        <v>2.587932195882628</v>
       </c>
       <c r="M42" t="n">
-        <v>0.488549623568005</v>
+        <v>1.608705130184717</v>
       </c>
       <c r="N42" t="n">
-        <v>0.4358010789734625</v>
+        <v>0.9692655164506987</v>
       </c>
       <c r="O42" t="n">
-        <v>0.08713100433691745</v>
+        <v>0.9874689949367369</v>
       </c>
       <c r="P42" t="n">
-        <v>0.09557725443316351</v>
-      </c>
-      <c r="Q42" t="inlineStr">
+        <v>0.9876721872776174</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.9291046014397268</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.083294075166219</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.8986848601331401</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.309019565558417</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.51954584187461</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.9434102680636589</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.9753656161929036</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.9669653132236636</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.8656576859148946</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.261261699811448</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.080926089242194</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>3.072218350873398</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.752774472336187</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9606582965298807</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.9804385078476577</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.9780838731419427</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.8801674568906994</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.009837270628836992</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.2109464642861286</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.005153511961889734</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.005252249705772927</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.01243108043515812</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0.1467409387434025</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0.1384529563486541</v>
+      </c>
+      <c r="AO42" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="AP42" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S42" t="n">
+      <c r="AQ42" t="n">
         <v>2</v>
       </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="n">
+      <c r="AR42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3364,67 +6436,139 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>1.167871201011295</v>
+        <v>1.224474866039086</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8722558942126972</v>
+        <v>0.9346494750511694</v>
       </c>
       <c r="D43" t="n">
-        <v>2.415121848947217</v>
+        <v>2.657291121826498</v>
       </c>
       <c r="E43" t="n">
-        <v>1.554066230553646</v>
+        <v>1.63011997160531</v>
       </c>
       <c r="F43" t="n">
-        <v>0.961863177372615</v>
+        <v>0.9624125143812329</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9808864566886235</v>
+        <v>0.9812276458016674</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9806214806547942</v>
+        <v>0.9776036833071676</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8820870360135712</v>
+        <v>0.8753023140627696</v>
       </c>
       <c r="J43" t="n">
-        <v>0.004953378704242617</v>
+        <v>1.372881067901105</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1028464413206769</v>
+        <v>1.021470168603124</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4917080189787773</v>
+        <v>2.784713125781224</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4883270560764694</v>
+        <v>1.66874597401199</v>
       </c>
       <c r="N43" t="n">
-        <v>0.4348061377119712</v>
+        <v>0.966928530859497</v>
       </c>
       <c r="O43" t="n">
-        <v>0.07698273610872852</v>
+        <v>0.9862533534035467</v>
       </c>
       <c r="P43" t="n">
-        <v>0.09489739081821796</v>
-      </c>
-      <c r="Q43" t="inlineStr">
+        <v>0.9865357889606001</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.9225692818516397</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.078179435951813</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.8157259002972008</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.292173749569804</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.513992651755551</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.9438231273677826</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.9768320803970024</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.9622508760902261</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.8516954651743317</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.257560800620532</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.9132057019574602</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.828215771648596</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.681729993681684</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.9637829042307224</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.9819999938560028</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.9786455325316022</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.8784759114898844</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.008924749902051998</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.1820609804362614</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.004667293945165962</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.004758996913836133</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.01383684286462017</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0.136136149459358</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0.1512403212671162</v>
+      </c>
+      <c r="AO43" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="AP43" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S43" t="n">
+      <c r="AQ43" t="n">
         <v>3</v>
       </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
+      <c r="AR43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3433,67 +6577,139 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>1.194765442809171</v>
+        <v>1.266074711302379</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9513404762039843</v>
+        <v>1.046451166734741</v>
       </c>
       <c r="D44" t="n">
-        <v>2.52721972393813</v>
+        <v>2.84139596910586</v>
       </c>
       <c r="E44" t="n">
-        <v>1.58972315952751</v>
+        <v>1.685644081384282</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9600930568392354</v>
+        <v>0.9598083442010752</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9803034200334767</v>
+        <v>0.9802156610959162</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9801160955175854</v>
+        <v>0.9772103070138123</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8800484816918873</v>
+        <v>0.8742688121316844</v>
       </c>
       <c r="J44" t="n">
-        <v>0.00432263688446749</v>
+        <v>1.380622123838035</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0907058862881166</v>
+        <v>1.106699908966074</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4915023342323848</v>
+        <v>3.071303021115593</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4872274982317464</v>
+        <v>1.752513344062062</v>
       </c>
       <c r="N44" t="n">
-        <v>0.4327836226842125</v>
+        <v>0.9635249670267336</v>
       </c>
       <c r="O44" t="n">
-        <v>0.07059122161509612</v>
+        <v>0.9835106478806473</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1225412663254938</v>
-      </c>
-      <c r="Q44" t="inlineStr">
+        <v>0.985399390643583</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.9203908419889439</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.136467397965992</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.8101522709264026</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.611372801312685</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.615974257626861</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.936000158241882</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.9729091330830255</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.9595918682952422</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.8451250083552433</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.301542813853213</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.078650392175103</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.894666694665201</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.701372003609205</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.9629319580380823</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.9813800732223722</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.9780294092011272</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.8781939872564153</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.007798463672735234</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.1503990454364074</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.003788730201003232</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.004126495376662487</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0.01128374985045422</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.1351714042662538</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0.199597506032453</v>
+      </c>
+      <c r="AO44" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="AP44" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S44" t="n">
+      <c r="AQ44" t="n">
         <v>4</v>
       </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
+      <c r="AR44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3502,67 +6718,139 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>1.444503188908976</v>
+        <v>1.520885832686467</v>
       </c>
       <c r="C45" t="n">
-        <v>1.050538735981218</v>
+        <v>1.196947673817825</v>
       </c>
       <c r="D45" t="n">
-        <v>3.716664537200918</v>
+        <v>4.144180763300114</v>
       </c>
       <c r="E45" t="n">
-        <v>1.92786527983698</v>
+        <v>2.035726102229893</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9413107142885935</v>
+        <v>0.9413804029364137</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9717406186886748</v>
+        <v>0.9717728528603472</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9722214396800047</v>
+        <v>0.9698606206090963</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8567654427256886</v>
+        <v>0.8518270559138313</v>
       </c>
       <c r="J45" t="n">
-        <v>0.006237474247015318</v>
+        <v>1.380504169561549</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1217443702612723</v>
+        <v>0.8391981902559618</v>
       </c>
       <c r="L45" t="n">
-        <v>0.48787975686248</v>
+        <v>3.107543714194632</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4827907845939318</v>
+        <v>1.762822655344159</v>
       </c>
       <c r="N45" t="n">
-        <v>0.4207292034307547</v>
+        <v>0.9630945697439048</v>
       </c>
       <c r="O45" t="n">
-        <v>0.09732240904331357</v>
+        <v>0.9815829096425009</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1730042766725351</v>
-      </c>
-      <c r="Q45" t="inlineStr">
+        <v>0.9791491998999878</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.896428003499291</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.443517512344907</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.993714060710819</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4.071448549662571</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2.017783077950296</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.9002164444794174</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.9591909362698937</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.9466394008767326</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.8139153384645735</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.617971057827696</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.385371387669938</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>4.564418362825275</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.136449943908182</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.9415497294673769</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0.9718146254848741</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0.9695670743969244</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0.8491557912090925</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0.01369825220336646</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0.2155108072366019</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.006058233247571265</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0.006078562407308696</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0.01279585671743982</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0.174609092484638</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0.2849758119057713</v>
+      </c>
+      <c r="AO45" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="AP45" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="S45" t="n">
+      <c r="AQ45" t="n">
         <v>7</v>
       </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="AR45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3571,67 +6859,139 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>1.346641279514074</v>
+        <v>1.424076637628607</v>
       </c>
       <c r="C46" t="n">
-        <v>1.037270341907009</v>
+        <v>1.144173227345542</v>
       </c>
       <c r="D46" t="n">
-        <v>3.318216517138954</v>
+        <v>3.769518447947091</v>
       </c>
       <c r="E46" t="n">
-        <v>1.821597243393543</v>
+        <v>1.941524773972017</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9476025465097958</v>
+        <v>0.946680015867249</v>
       </c>
       <c r="G46" t="n">
-        <v>0.974016615118027</v>
+        <v>0.9732199691442249</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9789202447058017</v>
+        <v>0.9748009907782985</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8785596498839159</v>
+        <v>0.8703562691068613</v>
       </c>
       <c r="J46" t="n">
-        <v>0.007891444906010125</v>
+        <v>1.747235301400421</v>
       </c>
       <c r="K46" t="n">
-        <v>0.137650577791406</v>
+        <v>1.47768306881123</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4881427428385471</v>
+        <v>5.369061798516883</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4853700071089277</v>
+        <v>2.317123604496938</v>
       </c>
       <c r="N46" t="n">
-        <v>0.4266919883699433</v>
+        <v>0.9362366055091256</v>
       </c>
       <c r="O46" t="n">
-        <v>0.09716129925428219</v>
+        <v>0.9765666253768275</v>
       </c>
       <c r="P46" t="n">
-        <v>0.1053518758967605</v>
-      </c>
-      <c r="Q46" t="inlineStr">
+        <v>0.9831265940095483</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.9225692818516397</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.309393322059165</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.155912879828592</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.4921774838383</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.868736868539362</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.9144132901114059</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.9721531924130206</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.9621040597089079</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.8525167722767177</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.374805708000839</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.048301097628071</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>3.352895654482315</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.831091383432928</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.9570640457350974</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.9838123532335723</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.9824443924034811</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0.8979286835992561</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.009737671043225538</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0.2070660839533038</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0.00491050800843662</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.006456029601043134</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0.01541337596618131</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0.1629604671772652</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0.1778783969731412</v>
+      </c>
+      <c r="AO46" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="AP46" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S46" t="n">
+      <c r="AQ46" t="n">
         <v>2</v>
       </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" t="n">
+      <c r="AR46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3640,67 +7000,139 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>1.38496003908732</v>
+        <v>1.443712905256562</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9854648786837235</v>
+        <v>1.072418216936885</v>
       </c>
       <c r="D47" t="n">
-        <v>3.714513353876416</v>
+        <v>4.187949097300576</v>
       </c>
       <c r="E47" t="n">
-        <v>1.927307280605876</v>
+        <v>2.046447921961509</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9413446832980334</v>
+        <v>0.9407612981603931</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9707322706360256</v>
+        <v>0.970407628351417</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9777611168938946</v>
+        <v>0.9735318298503147</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8746199718689762</v>
+        <v>0.866296082949026</v>
       </c>
       <c r="J47" t="n">
-        <v>0.009681855940225692</v>
+        <v>1.904736218772989</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1567635134383043</v>
+        <v>1.210838566652127</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4875825356151249</v>
+        <v>7.180529901811767</v>
       </c>
       <c r="M47" t="n">
-        <v>0.484109014146842</v>
+        <v>2.679651078370422</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4241260651081494</v>
+        <v>0.9147234697672471</v>
       </c>
       <c r="O47" t="n">
-        <v>0.1150207236932715</v>
+        <v>0.970771402624614</v>
       </c>
       <c r="P47" t="n">
-        <v>0.1152815503523489</v>
-      </c>
-      <c r="Q47" t="inlineStr">
+        <v>0.9790071501103607</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.9094986426754653</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.367281546787058</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.9933723017666289</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.983839107412774</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.995955687737775</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.9023635873299846</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.9736361429204891</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.9618430528087869</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.8516954651743317</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.321547880587813</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.9466364426438822</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>3.221191773940489</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.794767888597433</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.9587505974128672</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.9838684875340763</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.9818112490915011</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0.8942636685641571</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0.01474232009819987</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0.2523193376556132</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0.006198933424677977</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.006304892558926578</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0.01772143462775738</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0.1692856896175831</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0.1882397574669329</v>
+      </c>
+      <c r="AO47" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="AP47" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S47" t="n">
+      <c r="AQ47" t="n">
         <v>3</v>
       </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
+      <c r="AR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS47" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3709,67 +7141,139 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>1.291666570955957</v>
+        <v>1.395118725541672</v>
       </c>
       <c r="C48" t="n">
-        <v>0.838900879824691</v>
+        <v>0.8985473958628072</v>
       </c>
       <c r="D48" t="n">
-        <v>3.606200519700087</v>
+        <v>4.224015006794668</v>
       </c>
       <c r="E48" t="n">
-        <v>1.898999873538723</v>
+        <v>2.055240863449992</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9430550348262815</v>
+        <v>0.940251144476703</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9720098384495381</v>
+        <v>0.9706014572417796</v>
       </c>
       <c r="H48" t="n">
-        <v>0.978990111410862</v>
+        <v>0.9739256603888122</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8780671901320484</v>
+        <v>0.8664437260820381</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0102721496968699</v>
+        <v>1.994808171508489</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2008018815455687</v>
+        <v>1.318332124150428</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4886493336841852</v>
+        <v>8.482241099612088</v>
       </c>
       <c r="M48" t="n">
-        <v>0.484841140841364</v>
+        <v>2.912428728675105</v>
       </c>
       <c r="N48" t="n">
-        <v>0.4272769925435427</v>
+        <v>0.8992642465857486</v>
       </c>
       <c r="O48" t="n">
-        <v>0.1195529328043786</v>
+        <v>0.9640001994464937</v>
       </c>
       <c r="P48" t="n">
-        <v>0.1223361208530522</v>
-      </c>
-      <c r="Q48" t="inlineStr">
+        <v>0.9757400049489362</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.9029633230873781</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.344495700846768</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.8835001619186481</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4.091177590662921</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.022665961216266</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.8997329227465468</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.9741428596028189</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.9577485070631371</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.8328054018194526</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.207172627653186</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.8420650107382706</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.754612906608878</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.659702656082974</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.9647254355746032</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0.9852767726975682</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0.9827065001186553</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0.8962371381984412</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0.0154764242133576</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0.2653322647232645</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0.006681477373155775</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0.006906611163131238</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0.01804661589863399</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0.1769341149401574</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0.1775721285656406</v>
+      </c>
+      <c r="AO48" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="AP48" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S48" t="n">
+      <c r="AQ48" t="n">
         <v>4</v>
       </c>
-      <c r="T48" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" t="n">
+      <c r="AR48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3778,67 +7282,139 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>1.327536940657867</v>
+        <v>1.449866141506327</v>
       </c>
       <c r="C49" t="n">
-        <v>0.7860946062181355</v>
+        <v>0.8374511127246871</v>
       </c>
       <c r="D49" t="n">
-        <v>3.893194777647423</v>
+        <v>4.63666207123578</v>
       </c>
       <c r="E49" t="n">
-        <v>1.973118034393134</v>
+        <v>2.153290986196659</v>
       </c>
       <c r="F49" t="n">
-        <v>0.938523152049772</v>
+        <v>0.9344142358019599</v>
       </c>
       <c r="G49" t="n">
-        <v>0.969277683270138</v>
+        <v>0.9672845146294642</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9773849527501111</v>
+        <v>0.9714845469933273</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8733945487654921</v>
+        <v>0.8601688929290202</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01054350894220224</v>
+        <v>1.931909400050832</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1876124385204661</v>
+        <v>0.9924766922904613</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4873692764647239</v>
+        <v>8.359307916593369</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4830540256348436</v>
+        <v>2.891246775457496</v>
       </c>
       <c r="N49" t="n">
-        <v>0.4236120681445129</v>
+        <v>0.9007242106053481</v>
       </c>
       <c r="O49" t="n">
-        <v>0.1137885231753155</v>
+        <v>0.9595565089626109</v>
       </c>
       <c r="P49" t="n">
-        <v>0.08041753782999922</v>
-      </c>
-      <c r="Q49" t="inlineStr">
+        <v>0.975455905369682</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.8986064433619868</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.278297816143295</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.7950931801172918</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.783839541876453</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.945209382528383</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.9072652009715078</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9762636320972933</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.961190535558484</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.8369119373313829</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.376667927045005</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.826560940926683</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>3.790437318493117</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.946904547863895</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.9514610473686428</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0.9784344537854591</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.9768277985068861</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0.8773482145560079</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0.01394045922918363</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0.2894925352751161</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.006709505447677455</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.006510717473761585</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0.0151412855474089</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0.2018368995883022</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.1864243021437341</v>
+      </c>
+      <c r="AO49" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="AP49" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="S49" t="n">
+      <c r="AQ49" t="n">
         <v>7</v>
       </c>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" t="n">
+      <c r="AR49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3847,67 +7423,139 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>1.091550198795394</v>
+        <v>1.129032486059811</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7706244170450698</v>
+        <v>0.7692479926952203</v>
       </c>
       <c r="D50" t="n">
-        <v>2.301429734900547</v>
+        <v>2.64210507919672</v>
       </c>
       <c r="E50" t="n">
-        <v>1.517046385217191</v>
+        <v>1.625455345186917</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9636584722930018</v>
+        <v>0.96262732154115</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9817936283909592</v>
+        <v>0.9811434648295667</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9809915853626809</v>
+        <v>0.9776813592265251</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8837362035547087</v>
+        <v>0.8784766414225317</v>
       </c>
       <c r="J50" t="n">
-        <v>0.004049525439078605</v>
+        <v>1.373110718337361</v>
       </c>
       <c r="K50" t="n">
-        <v>0.09331527985972987</v>
+        <v>1.205423699928279</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4917203787966108</v>
+        <v>2.91841616170573</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4874182246737117</v>
+        <v>1.708337250576048</v>
       </c>
       <c r="N50" t="n">
-        <v>0.434063993322241</v>
+        <v>0.9653406632311832</v>
       </c>
       <c r="O50" t="n">
-        <v>0.07121604704615225</v>
+        <v>0.9879349662054036</v>
       </c>
       <c r="P50" t="n">
-        <v>0.07932026442290374</v>
-      </c>
-      <c r="Q50" t="inlineStr">
+        <v>0.985399390643583</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.9116770825381612</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.053611009393513</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.716226762504375</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.540630362596662</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.593935495117874</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.9377339225213954</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.9742037568076418</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.9667206192548</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.8656576859148946</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.085155660438004</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.5914954270659187</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>2.602009971467858</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.613074694943746</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.9666796128944806</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.9853616754286338</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0.9813449015982688</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0.8900348050621198</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0.007338998667824226</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0.1677740335047013</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0.003586396191756547</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0.005117208254467986</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0.01243740216800554</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0.1340828060481409</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0.1518465668282741</v>
+      </c>
+      <c r="AO50" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="AP50" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S50" t="n">
+      <c r="AQ50" t="n">
         <v>2</v>
       </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="n">
+      <c r="AR50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3916,67 +7564,139 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>1.153327154774323</v>
+        <v>1.137347543199176</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7947685821409767</v>
+        <v>0.7970484335881114</v>
       </c>
       <c r="D51" t="n">
-        <v>2.484308601552755</v>
+        <v>2.456719004471988</v>
       </c>
       <c r="E51" t="n">
-        <v>1.576168963516525</v>
+        <v>1.567392421977339</v>
       </c>
       <c r="F51" t="n">
-        <v>0.960770659861156</v>
+        <v>0.9652496147330402</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9801992366427209</v>
+        <v>0.9824952227184978</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9798702515207155</v>
+        <v>0.978454484458962</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8792811606831635</v>
+        <v>0.8799530727526536</v>
       </c>
       <c r="J51" t="n">
-        <v>0.005199114460716692</v>
+        <v>1.411514462089288</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1129925369437706</v>
+        <v>1.256679103175943</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4915665695051177</v>
+        <v>3.174016462308297</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4870232116018644</v>
+        <v>1.781576959412166</v>
       </c>
       <c r="N51" t="n">
-        <v>0.4330333383752654</v>
+        <v>0.9623051342298575</v>
       </c>
       <c r="O51" t="n">
-        <v>0.09191230893209257</v>
+        <v>0.9855193459350948</v>
       </c>
       <c r="P51" t="n">
-        <v>0.1077127225881314</v>
-      </c>
-      <c r="Q51" t="inlineStr">
+        <v>0.9822742952717852</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.9029633230873781</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.9798845765890962</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.7135560136163417</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.965084795418705</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.401814822085537</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.9518394631801093</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.9797609627843609</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.9705867839628438</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.8755133711435271</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.131347453651746</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.6970918126144756</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>2.488426235108673</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.577474638499356</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.9681341246395851</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0.9866069756910439</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0.98152531340222</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.8866517142604901</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0.008368000997618807</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0.1901813213685222</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0.004228920435664085</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0.005226009328491488</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0.01270539545519778</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0.1379910362287992</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0.1579698529140697</v>
+      </c>
+      <c r="AO51" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="AP51" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S51" t="n">
+      <c r="AQ51" t="n">
         <v>3</v>
       </c>
-      <c r="T51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
+      <c r="AR51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3985,67 +7705,139 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>1.161546984964975</v>
+        <v>1.111471232559655</v>
       </c>
       <c r="C52" t="n">
-        <v>0.7754306499600174</v>
+        <v>0.7847711269057456</v>
       </c>
       <c r="D52" t="n">
-        <v>2.719510893483132</v>
+        <v>2.496266375219571</v>
       </c>
       <c r="E52" t="n">
-        <v>1.649093961387019</v>
+        <v>1.579957713111199</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9570566161607053</v>
+        <v>0.9646902156453658</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9782945881134956</v>
+        <v>0.982218367348868</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9788008315435024</v>
+        <v>0.9781292449369731</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8767501466096123</v>
+        <v>0.8793625002206048</v>
       </c>
       <c r="J52" t="n">
-        <v>0.00607191499211901</v>
+        <v>1.321782326473771</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1220705197252535</v>
+        <v>0.9981917585552547</v>
       </c>
       <c r="L52" t="n">
-        <v>0.4904271745159284</v>
+        <v>2.998692830231132</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4862871694837468</v>
+        <v>1.731673419046193</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4313860271255945</v>
+        <v>0.9643872912873154</v>
       </c>
       <c r="O52" t="n">
-        <v>0.09858371369654262</v>
+        <v>0.987127586715796</v>
       </c>
       <c r="P52" t="n">
-        <v>0.09217913697042257</v>
-      </c>
-      <c r="Q52" t="inlineStr">
+        <v>0.9839788927473112</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.9116770825381612</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.9847532071668448</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.7337220628210062</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.074958690147726</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.440471690158375</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.949146660424229</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.9808556957828798</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.9749097107460998</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.8861903634745457</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.110396932527104</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.6492831456887593</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>2.564261328150679</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.601331111341649</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.96716300820112</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0.987072966083928</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0.9823592924959568</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0.8931359716302805</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0.007921024429448309</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0.1742313351412001</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0.004130140624656331</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0.00613056627234404</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0.01444195819955041</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0.1320867917036457</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0.1808180635177213</v>
+      </c>
+      <c r="AO52" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="AP52" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S52" t="n">
+      <c r="AQ52" t="n">
         <v>4</v>
       </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
+      <c r="AR52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4054,67 +7846,139 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>1.173795236031684</v>
+        <v>1.097712867064049</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7575971961536453</v>
+        <v>0.7146372377066192</v>
       </c>
       <c r="D53" t="n">
-        <v>2.723320536290352</v>
+        <v>2.373846802229678</v>
       </c>
       <c r="E53" t="n">
-        <v>1.650248628628532</v>
+        <v>1.540729308551531</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9569964586692412</v>
+        <v>0.9664218452366506</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9783374809008091</v>
+        <v>0.9830909960628934</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9787545543633052</v>
+        <v>0.9789087296014042</v>
       </c>
       <c r="I53" t="n">
-        <v>0.877631993142026</v>
+        <v>0.8826844707133791</v>
       </c>
       <c r="J53" t="n">
-        <v>0.005625102367919299</v>
+        <v>1.23920643581117</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1158663854960753</v>
+        <v>0.9976900210172492</v>
       </c>
       <c r="L53" t="n">
-        <v>0.4903250422841566</v>
+        <v>2.393007278102235</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4857371836373507</v>
+        <v>1.546934800856919</v>
       </c>
       <c r="N53" t="n">
-        <v>0.429669529363652</v>
+        <v>0.9715804598979815</v>
       </c>
       <c r="O53" t="n">
-        <v>0.07776819829708248</v>
+        <v>0.9872232913992555</v>
       </c>
       <c r="P53" t="n">
-        <v>0.07825694143462258</v>
-      </c>
-      <c r="Q53" t="inlineStr">
+        <v>0.9802855982170052</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.8942495636365952</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.007377112624952</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.6351064119232739</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.482298223782409</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.575531092610492</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.9391635336637219</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.9750650230671802</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.9714839951820101</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.8796199066554574</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.100014167020591</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.7015978926147559</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>2.302346279170262</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.517348436968339</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.9705169964319436</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0.9866011756728638</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0.9817159371950741</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0.8894709565951815</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0.007829751744438396</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0.2031351110914081</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0.003938958883225596</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0.004967539894751183</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0.011837119737789</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0.144800781570021</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0.1043051825519479</v>
+      </c>
+      <c r="AO53" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="AP53" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S53" t="n">
+      <c r="AQ53" t="n">
         <v>7</v>
       </c>
-      <c r="T53" t="n">
-        <v>1</v>
-      </c>
-      <c r="U53" t="n">
+      <c r="AR53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4123,67 +7987,139 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>1.119598989780576</v>
+        <v>1.174596350237322</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7574262772200953</v>
+        <v>0.8254097387015722</v>
       </c>
       <c r="D54" t="n">
-        <v>2.518077303410273</v>
+        <v>2.669105561558234</v>
       </c>
       <c r="E54" t="n">
-        <v>1.586845078578962</v>
+        <v>1.633739747192996</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9602374234144488</v>
+        <v>0.9622453986746161</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9799678936579205</v>
+        <v>0.9810512808718921</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9810857179947508</v>
+        <v>0.9786470843993574</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8841370428876241</v>
+        <v>0.8810603962502451</v>
       </c>
       <c r="J54" t="n">
-        <v>0.00656870499378065</v>
+        <v>1.642338279867381</v>
       </c>
       <c r="K54" t="n">
-        <v>0.122808888668006</v>
+        <v>1.38051718034716</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4911915814268745</v>
+        <v>4.425205959139593</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4870145278067884</v>
+        <v>2.103617350931389</v>
       </c>
       <c r="N54" t="n">
-        <v>0.4332997204528775</v>
+        <v>0.9474459106889158</v>
       </c>
       <c r="O54" t="n">
-        <v>0.09672805696772768</v>
+        <v>0.9782556561078055</v>
       </c>
       <c r="P54" t="n">
-        <v>0.08638769510951594</v>
-      </c>
-      <c r="Q54" t="inlineStr">
+        <v>0.9730410589460201</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.872465165009638</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.007094442362855</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.7430041129539016</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.920233069504701</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.385724745216272</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.9529386947259199</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.9810915572368866</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.970847790862965</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.8755133711435271</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.104178932578141</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.7630012025808124</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>2.476133676717527</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.573573537117833</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.9682915386420685</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0.9850206457407874</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0.9822061126624133</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0.8942636685641571</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0.006846270933893783</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0.1769225527524458</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0.003381632155368131</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0.004615288456200517</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.01315365281584258</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0.1392001439884269</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0.1613088907814409</v>
+      </c>
+      <c r="AO54" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="AP54" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S54" t="n">
+      <c r="AQ54" t="n">
         <v>2</v>
       </c>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="n">
+      <c r="AR54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4192,67 +8128,139 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>1.286141233669597</v>
+        <v>1.284872872616962</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9134153238165474</v>
+        <v>0.9014513424695956</v>
       </c>
       <c r="D55" t="n">
-        <v>3.222948954671525</v>
+        <v>3.22668297340373</v>
       </c>
       <c r="E55" t="n">
-        <v>1.795257350541009</v>
+        <v>1.796297017033578</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9491069021320795</v>
+        <v>0.9543584446344857</v>
       </c>
       <c r="G55" t="n">
-        <v>0.974231588637911</v>
+        <v>0.9769209459758698</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9772474458303898</v>
+        <v>0.9750244793883801</v>
       </c>
       <c r="I55" t="n">
-        <v>0.872134768004901</v>
+        <v>0.8702824475403551</v>
       </c>
       <c r="J55" t="n">
-        <v>0.007788024847094899</v>
+        <v>2.008501361792565</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1411840765260333</v>
+        <v>1.346666806193045</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4887661828041208</v>
+        <v>7.142157068154884</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4849720971005972</v>
+        <v>2.67248144393088</v>
       </c>
       <c r="N55" t="n">
-        <v>0.4263096418547587</v>
+        <v>0.9151791885170056</v>
       </c>
       <c r="O55" t="n">
-        <v>0.1031044613260745</v>
+        <v>0.9618483030932399</v>
       </c>
       <c r="P55" t="n">
-        <v>0.1029680627718635</v>
-      </c>
-      <c r="Q55" t="inlineStr">
+        <v>0.9636657728306278</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.8528592062453765</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.9790501458314631</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.618053243603619</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.920133426160593</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.385688791237265</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.9529411367970987</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.9811837006026113</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.9716634374258435</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.8746920640411411</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.203712399929601</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.9322183590284956</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>2.580325181936418</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.606339061946891</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.966957300370475</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0.9860220442062322</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0.9818793290175206</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0.8889071081282431</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0.009965174209380756</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0.2135136503829065</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0.005159428478679451</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0.005795128550796669</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0.01370084091355961</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0.1616205180890948</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0.1810244492287617</v>
+      </c>
+      <c r="AO55" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="AP55" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S55" t="n">
+      <c r="AQ55" t="n">
         <v>3</v>
       </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
+      <c r="AR55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4261,67 +8269,139 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>1.201442195162153</v>
+        <v>1.171985148955697</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8327665098760734</v>
+        <v>0.7328385915602874</v>
       </c>
       <c r="D56" t="n">
-        <v>2.839602634555213</v>
+        <v>2.823453094206758</v>
       </c>
       <c r="E56" t="n">
-        <v>1.685112054005671</v>
+        <v>1.680313391664412</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9551602657010891</v>
+        <v>0.9600621468599896</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9773579758773105</v>
+        <v>0.9799030256297774</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9790279617476494</v>
+        <v>0.9771567060870042</v>
       </c>
       <c r="I56" t="n">
-        <v>0.877654898246764</v>
+        <v>0.8778122473239769</v>
       </c>
       <c r="J56" t="n">
-        <v>0.006877426071760451</v>
+        <v>1.758189842377541</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1340173375753029</v>
+        <v>1.276830223387947</v>
       </c>
       <c r="L56" t="n">
-        <v>0.4901077389491399</v>
+        <v>5.577345086231022</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4860049720969603</v>
+        <v>2.361640338034355</v>
       </c>
       <c r="N56" t="n">
-        <v>0.4303015915698895</v>
+        <v>0.9337630170240682</v>
       </c>
       <c r="O56" t="n">
-        <v>0.1006977300655707</v>
+        <v>0.9721807527999291</v>
       </c>
       <c r="P56" t="n">
-        <v>0.1171168555657636</v>
-      </c>
-      <c r="Q56" t="inlineStr">
+        <v>0.9635237230410008</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.8550376461080722</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.9100104961786778</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.5899792966063504</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.067419424299384</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.437852365265427</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.9493314336672619</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.9802944561654903</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.9770467047408413</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.8919395131912481</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.114705549694409</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.762835686726433</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>2.271909099035382</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.507285340947553</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.9709067638177782</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0.9868060310453882</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.982046124836268</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0.8917263504629347</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0.008725539422903938</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0.1794142602132531</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0.004354186359407763</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0.005599905102868175</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0.01389460455414659</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0.1292550798352184</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0.1478415805248761</v>
+      </c>
+      <c r="AO56" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="AP56" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S56" t="n">
+      <c r="AQ56" t="n">
         <v>4</v>
       </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="n">
+      <c r="AR56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4330,67 +8410,139 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>1.240114988568069</v>
+        <v>1.285941131994404</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8743986115355273</v>
+        <v>0.8817566987552077</v>
       </c>
       <c r="D57" t="n">
-        <v>2.956277172152941</v>
+        <v>3.282124834250619</v>
       </c>
       <c r="E57" t="n">
-        <v>1.71938278814025</v>
+        <v>1.811663554374989</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9533178757829837</v>
+        <v>0.9535742173700573</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9764218493739609</v>
+        <v>0.976569390110438</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9778293207770111</v>
+        <v>0.9730662285793115</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8739099136220976</v>
+        <v>0.8651149378849285</v>
       </c>
       <c r="J57" t="n">
-        <v>0.005887129694109094</v>
+        <v>2.066165821722536</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1083843472001312</v>
+        <v>1.846132303268996</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4894367363512132</v>
+        <v>6.906233109886142</v>
       </c>
       <c r="M57" t="n">
-        <v>0.4856833034245099</v>
+        <v>2.627971291678458</v>
       </c>
       <c r="N57" t="n">
-        <v>0.4279470092939615</v>
+        <v>0.917981039750138</v>
       </c>
       <c r="O57" t="n">
-        <v>0.09072823037913968</v>
+        <v>0.9582107270967516</v>
       </c>
       <c r="P57" t="n">
-        <v>0.1118224907192534</v>
-      </c>
-      <c r="Q57" t="inlineStr">
+        <v>0.9530120386085912</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.8288963677557235</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.150127350717529</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.6170767092285674</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3.338302892623164</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.827102321333746</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.9181844672805231</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.9633223577441831</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.9632622778281954</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.8607298433005782</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.083037875001818</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.8680603260862014</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.930839013335031</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.389546333640959</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.9752743824703836</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0.9883388790742238</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0.9830605157339559</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0.8936998200972187</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0.01103030156428553</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0.1982265164168854</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.005674451227049904</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0.006833955980043327</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.01548709508619506</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0.1315301612040745</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0.1349993836944345</v>
+      </c>
+      <c r="AO57" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="AP57" t="inlineStr">
         <is>
           <t>XGB</t>
         </is>
       </c>
-      <c r="S57" t="n">
+      <c r="AQ57" t="n">
         <v>7</v>
       </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
+      <c r="AR57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4399,67 +8551,139 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>1.552935735912255</v>
+        <v>1.553261163242933</v>
       </c>
       <c r="C58" t="n">
-        <v>1.281484159958841</v>
+        <v>1.283573294530751</v>
       </c>
       <c r="D58" t="n">
-        <v>4.349274836375375</v>
+        <v>4.365159615326588</v>
       </c>
       <c r="E58" t="n">
-        <v>2.085491509542864</v>
+        <v>2.089296440270406</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9313212610515281</v>
+        <v>0.9382546485339801</v>
       </c>
       <c r="G58" t="n">
-        <v>0.96530699609527</v>
+        <v>0.9696187158625271</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9726678932801899</v>
+        <v>0.9715967455435106</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8558034283266917</v>
+        <v>0.8560348852046789</v>
       </c>
       <c r="J58" t="n">
-        <v>0.009538905148709087</v>
+        <v>2.116600094289854</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1524343684331173</v>
+        <v>1.780531887068625</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4846384488673808</v>
+        <v>7.174558527568926</v>
       </c>
       <c r="M58" t="n">
-        <v>0.4814739833365553</v>
+        <v>2.678536639205991</v>
       </c>
       <c r="N58" t="n">
-        <v>0.4179708056943337</v>
+        <v>0.9147943862710586</v>
       </c>
       <c r="O58" t="n">
-        <v>0.1094981708195225</v>
+        <v>0.9811397271944331</v>
       </c>
       <c r="P58" t="n">
-        <v>0.09305943135313766</v>
-      </c>
-      <c r="Q58" t="inlineStr">
+        <v>0.9829845442199211</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.9138555224008568</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.224329714794761</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.8068037222006041</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.906594233286228</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.704873670770426</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.9287648355332998</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.9670200721892055</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.9619409303963323</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.8492315438671735</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1.54413844689751</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.283573294530751</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>4.211466684485623</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.052185830885113</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.946069499445501</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0.9735644713165418</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0.971041004795243</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0.857613518213167</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0.01341128807527753</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0.2362319637305864</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0.006561408631909127</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0.005854510927621404</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0.01338617172355061</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0.1651097668840023</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>0.1657407957768616</v>
+      </c>
+      <c r="AO58" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="AP58" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S58" t="n">
+      <c r="AQ58" t="n">
         <v>2</v>
       </c>
-      <c r="T58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U58" t="n">
+      <c r="AR58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4468,67 +8692,139 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>1.399351966571254</v>
+        <v>1.447762860657876</v>
       </c>
       <c r="C59" t="n">
-        <v>1.082726960408734</v>
+        <v>1.133554373257287</v>
       </c>
       <c r="D59" t="n">
-        <v>3.514876794664721</v>
+        <v>3.836543200828408</v>
       </c>
       <c r="E59" t="n">
-        <v>1.87480046796045</v>
+        <v>1.958709575416531</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9444971139101439</v>
+        <v>0.9457319481473313</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9721636322925292</v>
+        <v>0.9725614680816307</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9762785279387939</v>
+        <v>0.9741341589091932</v>
       </c>
       <c r="I59" t="n">
-        <v>0.866774973496204</v>
+        <v>0.8629741124562518</v>
       </c>
       <c r="J59" t="n">
-        <v>0.00676886606852467</v>
+        <v>1.76208867994629</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1020958589026419</v>
+        <v>1.242941423544339</v>
       </c>
       <c r="L59" t="n">
-        <v>0.4867093782776933</v>
+        <v>6.219033154908948</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4837293029319886</v>
+        <v>2.493798940353642</v>
       </c>
       <c r="N59" t="n">
-        <v>0.4221380032828579</v>
+        <v>0.9261422797335231</v>
       </c>
       <c r="O59" t="n">
-        <v>0.09127314936006758</v>
+        <v>0.9788799115384743</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0868498532933053</v>
-      </c>
-      <c r="Q59" t="inlineStr">
+        <v>0.9829845442199211</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.9116770825381612</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.281950966583074</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1.035830618316647</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3.047433566683682</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.745689997302981</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.9253131280458721</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.9641176920767981</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0.955823581174744</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.8286988663075224</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.432127491440483</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1.166209912417894</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>3.439736057678627</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.854652543653023</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.9559519993238117</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0.9810900273734214</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0.9773179739742253</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0.8725555025870322</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0.01175194441824257</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0.207368963972294</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.005854979075151145</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>0.005154046995854034</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.01360395155961885</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>0.1781534163046057</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>0.1780079505314768</v>
+      </c>
+      <c r="AO59" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="AP59" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S59" t="n">
+      <c r="AQ59" t="n">
         <v>3</v>
       </c>
-      <c r="T59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="n">
+      <c r="AR59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4537,67 +8833,139 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>1.287875631523407</v>
+        <v>1.380783871665741</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9120327751529169</v>
+        <v>0.9177064005231834</v>
       </c>
       <c r="D60" t="n">
-        <v>3.052882622723622</v>
+        <v>3.732576504612666</v>
       </c>
       <c r="E60" t="n">
-        <v>1.747250017233831</v>
+        <v>1.93198770819399</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9517923937726832</v>
+        <v>0.9472025610834682</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9758591759666786</v>
+        <v>0.9733076909715459</v>
       </c>
       <c r="H60" t="n">
-        <v>0.9783828432003201</v>
+        <v>0.9753292778789591</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8726157752043994</v>
+        <v>0.8673295848801112</v>
       </c>
       <c r="J60" t="n">
-        <v>0.006219760383701534</v>
+        <v>1.523609233599845</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1179105278400291</v>
+        <v>1.067757570914368</v>
       </c>
       <c r="L60" t="n">
-        <v>0.488515832250442</v>
+        <v>4.807755051115078</v>
       </c>
       <c r="M60" t="n">
-        <v>0.4846336879230351</v>
+        <v>2.192659355922638</v>
       </c>
       <c r="N60" t="n">
-        <v>0.425365119913951</v>
+        <v>0.9429027279916155</v>
       </c>
       <c r="O60" t="n">
-        <v>0.09785812749793377</v>
+        <v>0.9827150630118002</v>
       </c>
       <c r="P60" t="n">
-        <v>0.1285062018454197</v>
-      </c>
-      <c r="Q60" t="inlineStr">
+        <v>0.9858255400124643</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.9247477217143355</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.084844618034129</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.7872871043127465</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2.415762081832373</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.554272203261827</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0.940794209511252</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.9734640759136741</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.9609132157271054</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.8426610870480852</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.504943461222564</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.9177064005231834</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>4.125161483076096</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.031049355155137</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.9471746922586411</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0.9781924070919307</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0.9759904154168483</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0.8691724117854024</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0.01163626721137262</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0.263187955868383</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.005966135499929581</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0.005599689668160879</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0.01528708467972495</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0.195185764994908</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>0.182311859219483</v>
+      </c>
+      <c r="AO60" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="AP60" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S60" t="n">
+      <c r="AQ60" t="n">
         <v>4</v>
       </c>
-      <c r="T60" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" t="n">
+      <c r="AR60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS60" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4606,67 +8974,139 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>1.108130482614243</v>
+        <v>1.192109296535367</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8403896176280119</v>
+        <v>0.9800932478492452</v>
       </c>
       <c r="D61" t="n">
-        <v>2.255442031068175</v>
+        <v>2.418888278544388</v>
       </c>
       <c r="E61" t="n">
-        <v>1.501812914802698</v>
+        <v>1.555277556754545</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9643846571456876</v>
+        <v>0.9657847318133899</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9821910838991439</v>
+        <v>0.982774702584327</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9821352968423299</v>
+        <v>0.9781028987187115</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8878247647504455</v>
+        <v>0.8761143512943368</v>
       </c>
       <c r="J61" t="n">
-        <v>0.005042935204850718</v>
+        <v>1.066850942538958</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1028679181951706</v>
+        <v>0.886309821648136</v>
       </c>
       <c r="L61" t="n">
-        <v>0.4918425986199697</v>
+        <v>1.891593105178801</v>
       </c>
       <c r="M61" t="n">
-        <v>0.4875511007671227</v>
+        <v>1.37535199319258</v>
       </c>
       <c r="N61" t="n">
-        <v>0.4343158098183223</v>
+        <v>0.9775352935190554</v>
       </c>
       <c r="O61" t="n">
-        <v>0.09010055513630666</v>
+        <v>0.9910746207262604</v>
       </c>
       <c r="P61" t="n">
-        <v>0.07860076827532536</v>
-      </c>
-      <c r="Q61" t="inlineStr">
+        <v>0.9858255400124643</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.9160339622635525</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.047898913906902</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.8796863360868323</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1.99834987999427</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.413630036464375</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.9510241984473846</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.9757831293722468</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0.9614841683211203</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.8434823941504712</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.323468925668355</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1.107802611827095</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>2.860869702707151</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.691410565979517</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.963364749944106</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0.9815392263881825</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0.9768277985068861</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0.8711458814196865</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0.007110279587793311</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0.1417777017269701</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0.003550488431213861</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>0.003753373171102525</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0.009716825721115541</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>0.1121756449729342</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>0.1045783594562717</v>
+      </c>
+      <c r="AO61" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="AP61" t="inlineStr">
         <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="S61" t="n">
+      <c r="AQ61" t="n">
         <v>7</v>
       </c>
-      <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
+      <c r="AR61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS61" t="n">
         <v>1</v>
       </c>
     </row>
